--- a/00-日文單字.xlsx
+++ b/00-日文單字.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://guandamachine-my.sharepoint.com/personal/ec03_gd_guandamachine_com_tw/Documents/Fly/日語/日語練習網站/database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="206" documentId="11_AD4DBB64A54DDB1B405E38AFBD9A2E1F4F90DF1A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D26C3D50-10E1-49F4-A84E-E50A2CBDCEBA}"/>
+  <xr:revisionPtr revIDLastSave="220" documentId="11_AD4DBB64A54DDB1B405E38AFBD9A2E1F4F90DF1A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F378DC1-25AF-4D3F-9D86-E2CA63939C41}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3422" uniqueCount="2978">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3546" uniqueCount="3080">
   <si>
     <t>わたし</t>
   </si>
@@ -9162,6 +9162,313 @@
   <si>
     <t>これで お願いします</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>*第23課</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>問老師</t>
+  </si>
+  <si>
+    <t>せんせい に ききます</t>
+  </si>
+  <si>
+    <t>先生 に 聞きます</t>
+  </si>
+  <si>
+    <t>まわします</t>
+  </si>
+  <si>
+    <t>回します</t>
+  </si>
+  <si>
+    <t>轉動</t>
+  </si>
+  <si>
+    <t>引きます</t>
+  </si>
+  <si>
+    <t>拉</t>
+  </si>
+  <si>
+    <t>変えます</t>
+  </si>
+  <si>
+    <t>改變,換</t>
+  </si>
+  <si>
+    <t>さわります</t>
+  </si>
+  <si>
+    <t>触ります</t>
+  </si>
+  <si>
+    <t>摸,碰觸</t>
+  </si>
+  <si>
+    <t>ドア に さわります</t>
+  </si>
+  <si>
+    <t>ドア に 触ります</t>
+  </si>
+  <si>
+    <t>摸門,碰觸門</t>
+  </si>
+  <si>
+    <t>出來</t>
+  </si>
+  <si>
+    <t>おつり が でます</t>
+  </si>
+  <si>
+    <t>お釣り が 出ます</t>
+  </si>
+  <si>
+    <t>零錢出來</t>
+  </si>
+  <si>
+    <t>うごきます</t>
+  </si>
+  <si>
+    <t>動きます</t>
+  </si>
+  <si>
+    <t>とけい が うごきます</t>
+  </si>
+  <si>
+    <t>時計 が 動きます</t>
+  </si>
+  <si>
+    <t>鐘錶轉動</t>
+  </si>
+  <si>
+    <t>あるきます</t>
+  </si>
+  <si>
+    <t>歩きます</t>
+  </si>
+  <si>
+    <t>走</t>
+  </si>
+  <si>
+    <t>みち を あるきます</t>
+  </si>
+  <si>
+    <t>道 を 歩きます</t>
+  </si>
+  <si>
+    <t>わたります</t>
+  </si>
+  <si>
+    <t>渡ります</t>
+  </si>
+  <si>
+    <t>過</t>
+  </si>
+  <si>
+    <t>はし を わたります</t>
+  </si>
+  <si>
+    <t>橋 を 渡ります</t>
+  </si>
+  <si>
+    <t>過橋</t>
+  </si>
+  <si>
+    <t>きを つけます</t>
+  </si>
+  <si>
+    <t>気を つけます</t>
+  </si>
+  <si>
+    <t>小心,注意</t>
+  </si>
+  <si>
+    <t>くるま に きを つけます</t>
+  </si>
+  <si>
+    <t>車 に 気を つけます</t>
+  </si>
+  <si>
+    <t>小心車輛,注意車輛</t>
+  </si>
+  <si>
+    <t>ひっこしします</t>
+  </si>
+  <si>
+    <t>引っ越しします</t>
+  </si>
+  <si>
+    <t>搬家</t>
+  </si>
+  <si>
+    <t>でんきや</t>
+  </si>
+  <si>
+    <t>電気屋</t>
+  </si>
+  <si>
+    <t>電器行</t>
+  </si>
+  <si>
+    <t>經營某種店鋪的人</t>
+  </si>
+  <si>
+    <t>サイズ</t>
+  </si>
+  <si>
+    <t>尺寸</t>
+  </si>
+  <si>
+    <t>おと</t>
+  </si>
+  <si>
+    <t>音</t>
+  </si>
+  <si>
+    <t>聲音</t>
+  </si>
+  <si>
+    <t>きかい</t>
+  </si>
+  <si>
+    <t>機械</t>
+  </si>
+  <si>
+    <t>機械,機器</t>
+  </si>
+  <si>
+    <t>つまみ</t>
+  </si>
+  <si>
+    <t>旋轉鈕</t>
+  </si>
+  <si>
+    <t>こしょう</t>
+  </si>
+  <si>
+    <t>故障</t>
+  </si>
+  <si>
+    <t>こしょう します</t>
+  </si>
+  <si>
+    <t>故障 します</t>
+  </si>
+  <si>
+    <t>發生故障</t>
+  </si>
+  <si>
+    <t>しんごう</t>
+  </si>
+  <si>
+    <t>信号</t>
+  </si>
+  <si>
+    <t>紅綠燈</t>
+  </si>
+  <si>
+    <t>かど</t>
+  </si>
+  <si>
+    <t>角</t>
+  </si>
+  <si>
+    <t>轉角</t>
+  </si>
+  <si>
+    <t>橋</t>
+  </si>
+  <si>
+    <t>ちゅうしゃじょう</t>
+  </si>
+  <si>
+    <t>駐車場</t>
+  </si>
+  <si>
+    <t>停車場</t>
+  </si>
+  <si>
+    <t>…め</t>
+  </si>
+  <si>
+    <t>…目</t>
+  </si>
+  <si>
+    <t>第…</t>
+  </si>
+  <si>
+    <t>[お]しょうがつ</t>
+  </si>
+  <si>
+    <t>[お]正月</t>
+  </si>
+  <si>
+    <t>新年</t>
+  </si>
+  <si>
+    <t>ごちそうさま[でした]</t>
+  </si>
+  <si>
+    <t>謝謝你的款待(用於飲食後)</t>
+  </si>
+  <si>
+    <t>たて もの</t>
+  </si>
+  <si>
+    <t>がいこくじん とう ろく しょう</t>
+  </si>
+  <si>
+    <t>外国人登録証</t>
+  </si>
+  <si>
+    <t>外國人登記證</t>
+  </si>
+  <si>
+    <t>しょう とく たい し</t>
+  </si>
+  <si>
+    <t>聖徳太子</t>
+  </si>
+  <si>
+    <t>聖德太子(574～622)</t>
+  </si>
+  <si>
+    <t>ほう りゅう じ</t>
+  </si>
+  <si>
+    <t>法隆寺</t>
+  </si>
+  <si>
+    <t>法隆寺.奈良的寺廟,由聖德太子於7世紀初建成</t>
+  </si>
+  <si>
+    <t>げんき ちゃ</t>
+  </si>
+  <si>
+    <t>元気茶</t>
+  </si>
+  <si>
+    <t>元氣茶(虛構的茶名)</t>
+  </si>
+  <si>
+    <t>ほんだ えき</t>
+  </si>
+  <si>
+    <t>本田駅</t>
+  </si>
+  <si>
+    <t>本田站(虛構的車站名)</t>
+  </si>
+  <si>
+    <t>としょかん まえ</t>
+  </si>
+  <si>
+    <t>図書館前</t>
+  </si>
+  <si>
+    <t>圖書館前(虛構的車站名)</t>
   </si>
 </sst>
 </file>
@@ -9530,7 +9837,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1295"/>
+  <dimension ref="A1:C1338"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="55.625" customWidth="1"/>
@@ -19258,3281 +19565,3739 @@
     </row>
     <row r="991" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A991" t="s">
-        <v>455</v>
+        <v>2978</v>
       </c>
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A992" t="s">
-        <v>457</v>
+        <v>1433</v>
       </c>
       <c r="B992" t="s">
-        <v>456</v>
+        <v>1434</v>
       </c>
       <c r="C992" t="s">
-        <v>456</v>
+        <v>2979</v>
       </c>
     </row>
     <row r="993" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A993" t="s">
-        <v>460</v>
+        <v>2980</v>
       </c>
       <c r="B993" t="s">
-        <v>459</v>
+        <v>2981</v>
       </c>
       <c r="C993" t="s">
-        <v>458</v>
+        <v>2979</v>
       </c>
     </row>
     <row r="994" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A994" t="s">
-        <v>463</v>
+        <v>2982</v>
       </c>
       <c r="B994" t="s">
-        <v>462</v>
+        <v>2983</v>
       </c>
       <c r="C994" t="s">
-        <v>461</v>
+        <v>2984</v>
       </c>
     </row>
     <row r="995" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A995" t="s">
-        <v>465</v>
+        <v>2046</v>
       </c>
       <c r="B995" t="s">
-        <v>464</v>
+        <v>2985</v>
       </c>
       <c r="C995" t="s">
-        <v>464</v>
+        <v>2986</v>
       </c>
     </row>
     <row r="996" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A996" t="s">
-        <v>380</v>
+        <v>2057</v>
       </c>
       <c r="B996" t="s">
-        <v>381</v>
+        <v>2987</v>
       </c>
       <c r="C996" t="s">
-        <v>382</v>
+        <v>2988</v>
       </c>
     </row>
     <row r="997" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A997" t="s">
-        <v>468</v>
+        <v>2989</v>
       </c>
       <c r="B997" t="s">
-        <v>467</v>
+        <v>2990</v>
       </c>
       <c r="C997" t="s">
-        <v>466</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="998" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A998" t="s">
-        <v>471</v>
+        <v>2992</v>
       </c>
       <c r="B998" t="s">
-        <v>470</v>
+        <v>2993</v>
       </c>
       <c r="C998" t="s">
-        <v>469</v>
+        <v>2994</v>
       </c>
     </row>
     <row r="999" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A999" t="s">
-        <v>397</v>
+        <v>2764</v>
       </c>
       <c r="B999" t="s">
-        <v>398</v>
+        <v>2765</v>
       </c>
       <c r="C999" t="s">
-        <v>399</v>
+        <v>2995</v>
       </c>
     </row>
     <row r="1000" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1000" t="s">
-        <v>473</v>
+        <v>2996</v>
       </c>
       <c r="B1000" t="s">
-        <v>472</v>
+        <v>2997</v>
       </c>
       <c r="C1000" t="s">
-        <v>472</v>
+        <v>2998</v>
       </c>
     </row>
     <row r="1001" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1001" t="s">
-        <v>475</v>
+        <v>2999</v>
       </c>
       <c r="B1001" t="s">
-        <v>474</v>
+        <v>3000</v>
       </c>
       <c r="C1001" t="s">
-        <v>474</v>
+        <v>2984</v>
       </c>
     </row>
     <row r="1002" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1002" t="s">
-        <v>161</v>
+        <v>3001</v>
       </c>
       <c r="B1002" t="s">
-        <v>162</v>
+        <v>3002</v>
       </c>
       <c r="C1002" t="s">
-        <v>163</v>
+        <v>3003</v>
       </c>
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1003" t="s">
-        <v>478</v>
+        <v>3004</v>
       </c>
       <c r="B1003" t="s">
-        <v>477</v>
+        <v>3005</v>
       </c>
       <c r="C1003" t="s">
-        <v>476</v>
+        <v>3006</v>
       </c>
     </row>
     <row r="1004" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1004" t="s">
-        <v>364</v>
+        <v>3007</v>
       </c>
       <c r="B1004" t="s">
-        <v>365</v>
+        <v>3008</v>
       </c>
       <c r="C1004" t="s">
-        <v>365</v>
+        <v>736</v>
       </c>
     </row>
     <row r="1005" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1005" t="s">
-        <v>481</v>
+        <v>3009</v>
       </c>
       <c r="B1005" t="s">
-        <v>480</v>
+        <v>3010</v>
       </c>
       <c r="C1005" t="s">
-        <v>479</v>
+        <v>3011</v>
       </c>
     </row>
     <row r="1006" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1006" t="s">
-        <v>484</v>
+        <v>3012</v>
       </c>
       <c r="B1006" t="s">
-        <v>483</v>
+        <v>3013</v>
       </c>
       <c r="C1006" t="s">
-        <v>482</v>
+        <v>3014</v>
       </c>
     </row>
     <row r="1007" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1007" t="s">
-        <v>487</v>
+        <v>3015</v>
       </c>
       <c r="B1007" t="s">
-        <v>486</v>
+        <v>3016</v>
       </c>
       <c r="C1007" t="s">
-        <v>485</v>
+        <v>3017</v>
       </c>
     </row>
     <row r="1008" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1008" t="s">
-        <v>490</v>
+        <v>3018</v>
       </c>
       <c r="B1008" t="s">
-        <v>489</v>
+        <v>3019</v>
       </c>
       <c r="C1008" t="s">
-        <v>488</v>
+        <v>3020</v>
       </c>
     </row>
     <row r="1009" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1009" t="s">
-        <v>493</v>
+        <v>3021</v>
       </c>
       <c r="B1009" t="s">
-        <v>492</v>
+        <v>3022</v>
       </c>
       <c r="C1009" t="s">
-        <v>491</v>
+        <v>3023</v>
       </c>
     </row>
     <row r="1010" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1010" t="s">
-        <v>496</v>
+        <v>3024</v>
       </c>
       <c r="B1010" t="s">
-        <v>495</v>
+        <v>3025</v>
       </c>
       <c r="C1010" t="s">
-        <v>494</v>
+        <v>3026</v>
       </c>
     </row>
     <row r="1011" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1011" t="s">
-        <v>499</v>
+        <v>1993</v>
       </c>
       <c r="B1011" t="s">
-        <v>498</v>
+        <v>1994</v>
       </c>
       <c r="C1011" t="s">
-        <v>497</v>
+        <v>3027</v>
       </c>
     </row>
     <row r="1012" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1012" t="s">
-        <v>502</v>
-      </c>
-      <c r="B1012" t="s">
-        <v>501</v>
+        <v>3028</v>
       </c>
       <c r="C1012" t="s">
-        <v>500</v>
+        <v>3029</v>
       </c>
     </row>
     <row r="1013" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1013" t="s">
-        <v>504</v>
+        <v>3030</v>
       </c>
       <c r="B1013" t="s">
-        <v>503</v>
+        <v>3031</v>
       </c>
       <c r="C1013" t="s">
-        <v>503</v>
+        <v>3032</v>
       </c>
     </row>
     <row r="1014" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1014" t="s">
-        <v>507</v>
+        <v>3033</v>
       </c>
       <c r="B1014" t="s">
-        <v>506</v>
+        <v>3034</v>
       </c>
       <c r="C1014" t="s">
-        <v>505</v>
+        <v>3035</v>
       </c>
     </row>
     <row r="1015" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1015" t="s">
-        <v>510</v>
-      </c>
-      <c r="B1015" t="s">
-        <v>509</v>
+        <v>3036</v>
       </c>
       <c r="C1015" t="s">
-        <v>508</v>
+        <v>3037</v>
       </c>
     </row>
     <row r="1016" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1016" t="s">
-        <v>512</v>
+        <v>3038</v>
       </c>
       <c r="B1016" t="s">
-        <v>390</v>
+        <v>3039</v>
       </c>
       <c r="C1016" t="s">
-        <v>511</v>
+        <v>3039</v>
       </c>
     </row>
     <row r="1017" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1017" t="s">
-        <v>515</v>
+        <v>3040</v>
       </c>
       <c r="B1017" t="s">
-        <v>514</v>
+        <v>3041</v>
       </c>
       <c r="C1017" t="s">
-        <v>513</v>
+        <v>3042</v>
       </c>
     </row>
     <row r="1018" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1018" t="s">
-        <v>517</v>
+        <v>463</v>
       </c>
       <c r="B1018" t="s">
-        <v>383</v>
+        <v>462</v>
       </c>
       <c r="C1018" t="s">
-        <v>516</v>
+        <v>461</v>
       </c>
     </row>
     <row r="1019" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1019" t="s">
-        <v>519</v>
+        <v>499</v>
       </c>
       <c r="B1019" t="s">
-        <v>518</v>
+        <v>498</v>
       </c>
       <c r="C1019" t="s">
-        <v>518</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1020" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1020" t="s">
-        <v>522</v>
+        <v>3043</v>
       </c>
       <c r="B1020" t="s">
-        <v>521</v>
+        <v>3044</v>
       </c>
       <c r="C1020" t="s">
-        <v>520</v>
+        <v>3045</v>
       </c>
     </row>
     <row r="1021" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1021" t="s">
-        <v>523</v>
+        <v>3046</v>
+      </c>
+      <c r="B1021" t="s">
+        <v>3047</v>
+      </c>
+      <c r="C1021" t="s">
+        <v>3048</v>
       </c>
     </row>
     <row r="1022" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1022" t="s">
-        <v>526</v>
+        <v>1590</v>
       </c>
       <c r="B1022" t="s">
-        <v>525</v>
+        <v>3049</v>
       </c>
       <c r="C1022" t="s">
-        <v>524</v>
+        <v>3049</v>
       </c>
     </row>
     <row r="1023" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1023" t="s">
-        <v>529</v>
+        <v>3050</v>
       </c>
       <c r="B1023" t="s">
-        <v>528</v>
+        <v>3051</v>
       </c>
       <c r="C1023" t="s">
-        <v>527</v>
+        <v>3052</v>
       </c>
     </row>
     <row r="1024" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1024" t="s">
-        <v>532</v>
+        <v>3053</v>
       </c>
       <c r="B1024" t="s">
-        <v>531</v>
+        <v>3054</v>
       </c>
       <c r="C1024" t="s">
-        <v>530</v>
+        <v>3055</v>
       </c>
     </row>
     <row r="1025" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1025" t="s">
-        <v>535</v>
+        <v>3056</v>
       </c>
       <c r="B1025" t="s">
-        <v>534</v>
+        <v>3057</v>
       </c>
       <c r="C1025" t="s">
-        <v>533</v>
+        <v>3058</v>
       </c>
     </row>
     <row r="1026" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1026" t="s">
-        <v>538</v>
-      </c>
-      <c r="B1026" t="s">
-        <v>537</v>
+        <v>3059</v>
       </c>
       <c r="C1026" t="s">
-        <v>536</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="1027" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1027" t="s">
-        <v>541</v>
+        <v>3061</v>
       </c>
       <c r="B1027" t="s">
-        <v>540</v>
+        <v>467</v>
       </c>
       <c r="C1027" t="s">
-        <v>539</v>
+        <v>466</v>
       </c>
     </row>
     <row r="1028" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1028" t="s">
-        <v>543</v>
+        <v>3062</v>
       </c>
       <c r="B1028" t="s">
-        <v>542</v>
+        <v>3063</v>
       </c>
       <c r="C1028" t="s">
-        <v>542</v>
+        <v>3064</v>
       </c>
     </row>
     <row r="1029" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1029" t="s">
-        <v>545</v>
+        <v>3065</v>
       </c>
       <c r="B1029" t="s">
-        <v>544</v>
+        <v>3066</v>
       </c>
       <c r="C1029" t="s">
-        <v>544</v>
+        <v>3067</v>
       </c>
     </row>
     <row r="1030" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1030" t="s">
-        <v>547</v>
+        <v>3068</v>
       </c>
       <c r="B1030" t="s">
-        <v>546</v>
+        <v>3069</v>
       </c>
       <c r="C1030" t="s">
-        <v>546</v>
+        <v>3070</v>
       </c>
     </row>
     <row r="1031" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1031" t="s">
-        <v>549</v>
+        <v>3071</v>
       </c>
       <c r="B1031" t="s">
-        <v>548</v>
+        <v>3072</v>
       </c>
       <c r="C1031" t="s">
-        <v>548</v>
+        <v>3073</v>
       </c>
     </row>
     <row r="1032" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1032" t="s">
-        <v>552</v>
+        <v>3074</v>
       </c>
       <c r="B1032" t="s">
-        <v>551</v>
+        <v>3075</v>
       </c>
       <c r="C1032" t="s">
-        <v>550</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="1033" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1033" t="s">
-        <v>554</v>
+        <v>3077</v>
       </c>
       <c r="B1033" t="s">
-        <v>553</v>
+        <v>3078</v>
       </c>
       <c r="C1033" t="s">
-        <v>553</v>
+        <v>3079</v>
       </c>
     </row>
     <row r="1034" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1034" t="s">
-        <v>557</v>
-      </c>
-      <c r="B1034" t="s">
-        <v>556</v>
-      </c>
-      <c r="C1034" t="s">
-        <v>555</v>
+        <v>455</v>
       </c>
     </row>
     <row r="1035" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1035" t="s">
-        <v>559</v>
+        <v>457</v>
       </c>
       <c r="B1035" t="s">
-        <v>1126</v>
+        <v>456</v>
       </c>
       <c r="C1035" t="s">
-        <v>558</v>
+        <v>456</v>
       </c>
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1036" t="s">
-        <v>562</v>
+        <v>460</v>
       </c>
       <c r="B1036" t="s">
-        <v>561</v>
+        <v>459</v>
       </c>
       <c r="C1036" t="s">
-        <v>560</v>
+        <v>458</v>
       </c>
     </row>
     <row r="1037" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1037" t="s">
-        <v>565</v>
+        <v>463</v>
       </c>
       <c r="B1037" t="s">
-        <v>564</v>
+        <v>462</v>
       </c>
       <c r="C1037" t="s">
-        <v>563</v>
+        <v>461</v>
       </c>
     </row>
     <row r="1038" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1038" t="s">
-        <v>567</v>
+        <v>465</v>
       </c>
       <c r="B1038" t="s">
-        <v>566</v>
+        <v>464</v>
       </c>
       <c r="C1038" t="s">
-        <v>566</v>
+        <v>464</v>
       </c>
     </row>
     <row r="1039" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1039" t="s">
-        <v>570</v>
+        <v>380</v>
       </c>
       <c r="B1039" t="s">
-        <v>569</v>
+        <v>381</v>
       </c>
       <c r="C1039" t="s">
-        <v>568</v>
+        <v>382</v>
       </c>
     </row>
     <row r="1040" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1040" t="s">
-        <v>572</v>
+        <v>468</v>
       </c>
       <c r="B1040" t="s">
-        <v>571</v>
+        <v>467</v>
       </c>
       <c r="C1040" t="s">
-        <v>571</v>
+        <v>466</v>
       </c>
     </row>
     <row r="1041" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1041" t="s">
-        <v>575</v>
+        <v>471</v>
       </c>
       <c r="B1041" t="s">
-        <v>574</v>
+        <v>470</v>
       </c>
       <c r="C1041" t="s">
-        <v>573</v>
+        <v>469</v>
       </c>
     </row>
     <row r="1042" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1042" t="s">
-        <v>578</v>
+        <v>397</v>
       </c>
       <c r="B1042" t="s">
-        <v>577</v>
+        <v>398</v>
       </c>
       <c r="C1042" t="s">
-        <v>576</v>
+        <v>399</v>
       </c>
     </row>
     <row r="1043" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1043" t="s">
-        <v>581</v>
+        <v>473</v>
       </c>
       <c r="B1043" t="s">
-        <v>580</v>
+        <v>472</v>
       </c>
       <c r="C1043" t="s">
-        <v>579</v>
+        <v>472</v>
       </c>
     </row>
     <row r="1044" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1044" t="s">
-        <v>582</v>
+        <v>475</v>
       </c>
       <c r="B1044" t="s">
-        <v>120</v>
+        <v>474</v>
       </c>
       <c r="C1044" t="s">
-        <v>121</v>
+        <v>474</v>
       </c>
     </row>
     <row r="1045" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1045" t="s">
-        <v>585</v>
+        <v>161</v>
       </c>
       <c r="B1045" t="s">
-        <v>584</v>
+        <v>162</v>
       </c>
       <c r="C1045" t="s">
-        <v>583</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1046" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1046" t="s">
-        <v>586</v>
+        <v>478</v>
+      </c>
+      <c r="B1046" t="s">
+        <v>477</v>
+      </c>
+      <c r="C1046" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1047" t="s">
-        <v>589</v>
+        <v>364</v>
       </c>
       <c r="B1047" t="s">
-        <v>588</v>
+        <v>365</v>
       </c>
       <c r="C1047" t="s">
-        <v>587</v>
+        <v>365</v>
       </c>
     </row>
     <row r="1048" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1048" t="s">
-        <v>592</v>
+        <v>481</v>
       </c>
       <c r="B1048" t="s">
-        <v>591</v>
+        <v>480</v>
       </c>
       <c r="C1048" t="s">
-        <v>590</v>
+        <v>479</v>
       </c>
     </row>
     <row r="1049" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1049" t="s">
-        <v>595</v>
+        <v>484</v>
       </c>
       <c r="B1049" t="s">
-        <v>594</v>
+        <v>483</v>
       </c>
       <c r="C1049" t="s">
-        <v>593</v>
+        <v>482</v>
       </c>
     </row>
     <row r="1050" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1050" t="s">
-        <v>598</v>
+        <v>487</v>
       </c>
       <c r="B1050" t="s">
-        <v>597</v>
+        <v>486</v>
       </c>
       <c r="C1050" t="s">
-        <v>596</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1051" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1051" t="s">
-        <v>601</v>
+        <v>490</v>
       </c>
       <c r="B1051" t="s">
-        <v>600</v>
+        <v>489</v>
       </c>
       <c r="C1051" t="s">
-        <v>599</v>
+        <v>488</v>
       </c>
     </row>
     <row r="1052" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1052" t="s">
-        <v>604</v>
+        <v>493</v>
       </c>
       <c r="B1052" t="s">
-        <v>603</v>
+        <v>492</v>
       </c>
       <c r="C1052" t="s">
-        <v>602</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1053" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1053" t="s">
-        <v>607</v>
+        <v>496</v>
       </c>
       <c r="B1053" t="s">
-        <v>606</v>
+        <v>495</v>
       </c>
       <c r="C1053" t="s">
-        <v>605</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1054" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1054" t="s">
-        <v>610</v>
+        <v>499</v>
       </c>
       <c r="B1054" t="s">
-        <v>609</v>
+        <v>498</v>
       </c>
       <c r="C1054" t="s">
-        <v>608</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1055" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1055" t="s">
-        <v>613</v>
+        <v>502</v>
       </c>
       <c r="B1055" t="s">
-        <v>612</v>
+        <v>501</v>
       </c>
       <c r="C1055" t="s">
-        <v>611</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1056" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1056" t="s">
-        <v>616</v>
+        <v>504</v>
       </c>
       <c r="B1056" t="s">
-        <v>615</v>
+        <v>503</v>
       </c>
       <c r="C1056" t="s">
-        <v>614</v>
+        <v>503</v>
       </c>
     </row>
     <row r="1057" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1057" t="s">
-        <v>619</v>
+        <v>507</v>
       </c>
       <c r="B1057" t="s">
-        <v>618</v>
+        <v>506</v>
       </c>
       <c r="C1057" t="s">
-        <v>617</v>
+        <v>505</v>
       </c>
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1058" t="s">
-        <v>404</v>
+        <v>510</v>
       </c>
       <c r="B1058" t="s">
-        <v>405</v>
+        <v>509</v>
       </c>
       <c r="C1058" t="s">
-        <v>406</v>
+        <v>508</v>
       </c>
     </row>
     <row r="1059" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1059" t="s">
-        <v>622</v>
+        <v>512</v>
       </c>
       <c r="B1059" t="s">
-        <v>621</v>
+        <v>390</v>
       </c>
       <c r="C1059" t="s">
-        <v>620</v>
+        <v>511</v>
       </c>
     </row>
     <row r="1060" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1060" t="s">
-        <v>58</v>
+        <v>515</v>
       </c>
       <c r="B1060" t="s">
-        <v>59</v>
+        <v>514</v>
       </c>
       <c r="C1060" t="s">
-        <v>623</v>
+        <v>513</v>
       </c>
     </row>
     <row r="1061" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1061" t="s">
-        <v>625</v>
+        <v>517</v>
       </c>
       <c r="B1061" t="s">
-        <v>624</v>
+        <v>383</v>
       </c>
       <c r="C1061" t="s">
-        <v>624</v>
+        <v>516</v>
       </c>
     </row>
     <row r="1062" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1062" t="s">
-        <v>628</v>
+        <v>519</v>
       </c>
       <c r="B1062" t="s">
-        <v>627</v>
+        <v>518</v>
       </c>
       <c r="C1062" t="s">
-        <v>626</v>
+        <v>518</v>
       </c>
     </row>
     <row r="1063" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1063" t="s">
-        <v>61</v>
+        <v>522</v>
       </c>
       <c r="B1063" t="s">
-        <v>62</v>
+        <v>521</v>
       </c>
       <c r="C1063" t="s">
-        <v>629</v>
+        <v>520</v>
       </c>
     </row>
     <row r="1064" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1064" t="s">
-        <v>632</v>
-      </c>
-      <c r="B1064" t="s">
-        <v>631</v>
-      </c>
-      <c r="C1064" t="s">
-        <v>630</v>
+        <v>523</v>
       </c>
     </row>
     <row r="1065" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1065" t="s">
-        <v>635</v>
+        <v>526</v>
       </c>
       <c r="B1065" t="s">
-        <v>634</v>
+        <v>525</v>
       </c>
       <c r="C1065" t="s">
-        <v>633</v>
+        <v>524</v>
       </c>
     </row>
     <row r="1066" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1066" t="s">
-        <v>638</v>
+        <v>529</v>
       </c>
       <c r="B1066" t="s">
-        <v>637</v>
+        <v>528</v>
       </c>
       <c r="C1066" t="s">
-        <v>636</v>
+        <v>527</v>
       </c>
     </row>
     <row r="1067" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1067" t="s">
-        <v>82</v>
+        <v>532</v>
       </c>
       <c r="B1067" t="s">
-        <v>83</v>
+        <v>531</v>
       </c>
       <c r="C1067" t="s">
-        <v>83</v>
+        <v>530</v>
       </c>
     </row>
     <row r="1068" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1068" t="s">
-        <v>641</v>
+        <v>535</v>
       </c>
       <c r="B1068" t="s">
-        <v>640</v>
+        <v>534</v>
       </c>
       <c r="C1068" t="s">
-        <v>639</v>
+        <v>533</v>
       </c>
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1069" t="s">
-        <v>644</v>
+        <v>538</v>
       </c>
       <c r="B1069" t="s">
-        <v>643</v>
+        <v>537</v>
       </c>
       <c r="C1069" t="s">
-        <v>642</v>
+        <v>536</v>
       </c>
     </row>
     <row r="1070" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1070" t="s">
-        <v>647</v>
+        <v>541</v>
       </c>
       <c r="B1070" t="s">
-        <v>646</v>
+        <v>540</v>
       </c>
       <c r="C1070" t="s">
-        <v>645</v>
+        <v>539</v>
       </c>
     </row>
     <row r="1071" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1071" t="s">
-        <v>650</v>
+        <v>543</v>
       </c>
       <c r="B1071" t="s">
-        <v>649</v>
+        <v>542</v>
       </c>
       <c r="C1071" t="s">
-        <v>648</v>
+        <v>542</v>
       </c>
     </row>
     <row r="1072" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1072" t="s">
-        <v>651</v>
+        <v>545</v>
       </c>
       <c r="B1072" t="s">
-        <v>70</v>
+        <v>544</v>
       </c>
       <c r="C1072" t="s">
-        <v>71</v>
+        <v>544</v>
       </c>
     </row>
     <row r="1073" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1073" t="s">
-        <v>652</v>
+        <v>547</v>
       </c>
       <c r="B1073" t="s">
-        <v>84</v>
+        <v>546</v>
       </c>
       <c r="C1073" t="s">
-        <v>85</v>
+        <v>546</v>
       </c>
     </row>
     <row r="1074" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1074" t="s">
-        <v>653</v>
+        <v>549</v>
       </c>
       <c r="B1074" t="s">
-        <v>86</v>
+        <v>548</v>
       </c>
       <c r="C1074" t="s">
-        <v>87</v>
+        <v>548</v>
       </c>
     </row>
     <row r="1075" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1075" t="s">
-        <v>402</v>
+        <v>552</v>
       </c>
       <c r="B1075" t="s">
-        <v>403</v>
+        <v>551</v>
       </c>
       <c r="C1075" t="s">
-        <v>403</v>
+        <v>550</v>
       </c>
     </row>
     <row r="1076" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1076" t="s">
-        <v>656</v>
+        <v>554</v>
       </c>
       <c r="B1076" t="s">
-        <v>655</v>
+        <v>553</v>
       </c>
       <c r="C1076" t="s">
-        <v>654</v>
+        <v>553</v>
       </c>
     </row>
     <row r="1077" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1077" t="s">
-        <v>659</v>
+        <v>557</v>
       </c>
       <c r="B1077" t="s">
-        <v>658</v>
+        <v>556</v>
       </c>
       <c r="C1077" t="s">
-        <v>657</v>
+        <v>555</v>
       </c>
     </row>
     <row r="1078" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1078" t="s">
-        <v>660</v>
+        <v>559</v>
       </c>
       <c r="B1078" t="s">
-        <v>102</v>
+        <v>1126</v>
       </c>
       <c r="C1078" t="s">
-        <v>103</v>
+        <v>558</v>
       </c>
     </row>
     <row r="1079" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1079" t="s">
-        <v>663</v>
+        <v>562</v>
       </c>
       <c r="B1079" t="s">
-        <v>662</v>
+        <v>561</v>
       </c>
       <c r="C1079" t="s">
-        <v>661</v>
+        <v>560</v>
       </c>
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1080" t="s">
-        <v>665</v>
+        <v>565</v>
       </c>
       <c r="B1080" t="s">
-        <v>106</v>
+        <v>564</v>
       </c>
       <c r="C1080" t="s">
-        <v>664</v>
+        <v>563</v>
       </c>
     </row>
     <row r="1081" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1081" t="s">
-        <v>667</v>
+        <v>567</v>
       </c>
       <c r="B1081" t="s">
-        <v>666</v>
+        <v>566</v>
       </c>
       <c r="C1081" t="s">
-        <v>109</v>
+        <v>566</v>
       </c>
     </row>
     <row r="1082" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1082" t="s">
-        <v>670</v>
+        <v>570</v>
       </c>
       <c r="B1082" t="s">
-        <v>669</v>
+        <v>569</v>
       </c>
       <c r="C1082" t="s">
-        <v>668</v>
+        <v>568</v>
       </c>
     </row>
     <row r="1083" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1083" t="s">
-        <v>671</v>
+        <v>572</v>
+      </c>
+      <c r="B1083" t="s">
+        <v>571</v>
+      </c>
+      <c r="C1083" t="s">
+        <v>571</v>
       </c>
     </row>
     <row r="1084" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1084" t="s">
-        <v>674</v>
+        <v>575</v>
       </c>
       <c r="B1084" t="s">
-        <v>673</v>
+        <v>574</v>
       </c>
       <c r="C1084" t="s">
-        <v>672</v>
+        <v>573</v>
       </c>
     </row>
     <row r="1085" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1085" t="s">
-        <v>677</v>
+        <v>578</v>
       </c>
       <c r="B1085" t="s">
-        <v>676</v>
+        <v>577</v>
       </c>
       <c r="C1085" t="s">
-        <v>675</v>
+        <v>576</v>
       </c>
     </row>
     <row r="1086" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1086" t="s">
-        <v>680</v>
+        <v>581</v>
       </c>
       <c r="B1086" t="s">
-        <v>679</v>
+        <v>580</v>
       </c>
       <c r="C1086" t="s">
-        <v>678</v>
+        <v>579</v>
       </c>
     </row>
     <row r="1087" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1087" t="s">
-        <v>683</v>
+        <v>582</v>
       </c>
       <c r="B1087" t="s">
-        <v>682</v>
+        <v>120</v>
       </c>
       <c r="C1087" t="s">
-        <v>681</v>
+        <v>121</v>
       </c>
     </row>
     <row r="1088" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1088" t="s">
-        <v>686</v>
+        <v>585</v>
       </c>
       <c r="B1088" t="s">
-        <v>685</v>
+        <v>584</v>
       </c>
       <c r="C1088" t="s">
-        <v>684</v>
+        <v>583</v>
       </c>
     </row>
     <row r="1089" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1089" t="s">
-        <v>689</v>
-      </c>
-      <c r="B1089" t="s">
-        <v>688</v>
-      </c>
-      <c r="C1089" t="s">
-        <v>687</v>
+        <v>586</v>
       </c>
     </row>
     <row r="1090" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1090" t="s">
-        <v>692</v>
+        <v>589</v>
       </c>
       <c r="B1090" t="s">
-        <v>691</v>
+        <v>588</v>
       </c>
       <c r="C1090" t="s">
-        <v>690</v>
+        <v>587</v>
       </c>
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1091" t="s">
-        <v>695</v>
+        <v>592</v>
       </c>
       <c r="B1091" t="s">
-        <v>694</v>
+        <v>591</v>
       </c>
       <c r="C1091" t="s">
-        <v>693</v>
+        <v>590</v>
       </c>
     </row>
     <row r="1092" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1092" t="s">
-        <v>698</v>
+        <v>595</v>
       </c>
       <c r="B1092" t="s">
-        <v>697</v>
+        <v>594</v>
       </c>
       <c r="C1092" t="s">
-        <v>696</v>
+        <v>593</v>
       </c>
     </row>
     <row r="1093" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1093" t="s">
-        <v>701</v>
+        <v>598</v>
       </c>
       <c r="B1093" t="s">
-        <v>700</v>
+        <v>597</v>
       </c>
       <c r="C1093" t="s">
-        <v>699</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1094" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1094" t="s">
-        <v>704</v>
+        <v>601</v>
       </c>
       <c r="B1094" t="s">
-        <v>703</v>
+        <v>600</v>
       </c>
       <c r="C1094" t="s">
-        <v>702</v>
+        <v>599</v>
       </c>
     </row>
     <row r="1095" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1095" t="s">
-        <v>400</v>
+        <v>604</v>
       </c>
       <c r="B1095" t="s">
-        <v>706</v>
+        <v>603</v>
       </c>
       <c r="C1095" t="s">
-        <v>705</v>
+        <v>602</v>
       </c>
     </row>
     <row r="1096" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1096" t="s">
-        <v>709</v>
+        <v>607</v>
       </c>
       <c r="B1096" t="s">
-        <v>708</v>
+        <v>606</v>
       </c>
       <c r="C1096" t="s">
-        <v>707</v>
+        <v>605</v>
       </c>
     </row>
     <row r="1097" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1097" t="s">
-        <v>712</v>
+        <v>610</v>
       </c>
       <c r="B1097" t="s">
-        <v>711</v>
+        <v>609</v>
       </c>
       <c r="C1097" t="s">
-        <v>710</v>
+        <v>608</v>
       </c>
     </row>
     <row r="1098" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1098" t="s">
-        <v>715</v>
+        <v>613</v>
       </c>
       <c r="B1098" t="s">
-        <v>714</v>
+        <v>612</v>
       </c>
       <c r="C1098" t="s">
-        <v>713</v>
+        <v>611</v>
       </c>
     </row>
     <row r="1099" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1099" t="s">
-        <v>718</v>
+        <v>616</v>
       </c>
       <c r="B1099" t="s">
-        <v>717</v>
+        <v>615</v>
       </c>
       <c r="C1099" t="s">
-        <v>716</v>
+        <v>614</v>
       </c>
     </row>
     <row r="1100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1100" t="s">
-        <v>719</v>
+        <v>619</v>
+      </c>
+      <c r="B1100" t="s">
+        <v>618</v>
+      </c>
+      <c r="C1100" t="s">
+        <v>617</v>
       </c>
     </row>
     <row r="1101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1101" t="s">
-        <v>720</v>
-      </c>
-      <c r="B1101">
-        <v>1</v>
+        <v>404</v>
+      </c>
+      <c r="B1101" t="s">
+        <v>405</v>
       </c>
       <c r="C1101" t="s">
-        <v>1127</v>
+        <v>406</v>
       </c>
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1102" t="s">
-        <v>721</v>
-      </c>
-      <c r="B1102">
-        <v>2</v>
+        <v>622</v>
+      </c>
+      <c r="B1102" t="s">
+        <v>621</v>
       </c>
       <c r="C1102" t="s">
-        <v>1128</v>
+        <v>620</v>
       </c>
     </row>
     <row r="1103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1103" t="s">
-        <v>722</v>
-      </c>
-      <c r="B1103">
-        <v>3</v>
+        <v>58</v>
+      </c>
+      <c r="B1103" t="s">
+        <v>59</v>
       </c>
       <c r="C1103" t="s">
-        <v>1129</v>
+        <v>623</v>
       </c>
     </row>
     <row r="1104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1104" t="s">
-        <v>723</v>
-      </c>
-      <c r="B1104">
-        <v>4</v>
+        <v>625</v>
+      </c>
+      <c r="B1104" t="s">
+        <v>624</v>
       </c>
       <c r="C1104" t="s">
-        <v>1130</v>
+        <v>624</v>
       </c>
     </row>
     <row r="1105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1105" t="s">
-        <v>724</v>
-      </c>
-      <c r="B1105">
-        <v>5</v>
+        <v>628</v>
+      </c>
+      <c r="B1105" t="s">
+        <v>627</v>
       </c>
       <c r="C1105" t="s">
-        <v>1131</v>
+        <v>626</v>
       </c>
     </row>
     <row r="1106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1106" t="s">
-        <v>725</v>
-      </c>
-      <c r="B1106">
-        <v>6</v>
+        <v>61</v>
+      </c>
+      <c r="B1106" t="s">
+        <v>62</v>
       </c>
       <c r="C1106" t="s">
-        <v>1132</v>
+        <v>629</v>
       </c>
     </row>
     <row r="1107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1107" t="s">
-        <v>726</v>
-      </c>
-      <c r="B1107">
-        <v>7</v>
+        <v>632</v>
+      </c>
+      <c r="B1107" t="s">
+        <v>631</v>
       </c>
       <c r="C1107" t="s">
-        <v>1133</v>
+        <v>630</v>
       </c>
     </row>
     <row r="1108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1108" t="s">
-        <v>727</v>
-      </c>
-      <c r="B1108">
-        <v>8</v>
+        <v>635</v>
+      </c>
+      <c r="B1108" t="s">
+        <v>634</v>
       </c>
       <c r="C1108" t="s">
-        <v>1134</v>
+        <v>633</v>
       </c>
     </row>
     <row r="1109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1109" t="s">
-        <v>728</v>
-      </c>
-      <c r="B1109">
-        <v>9</v>
+        <v>638</v>
+      </c>
+      <c r="B1109" t="s">
+        <v>637</v>
       </c>
       <c r="C1109" t="s">
-        <v>1135</v>
+        <v>636</v>
       </c>
     </row>
     <row r="1110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1110" t="s">
-        <v>729</v>
-      </c>
-      <c r="B1110">
-        <v>10</v>
+        <v>82</v>
+      </c>
+      <c r="B1110" t="s">
+        <v>83</v>
       </c>
       <c r="C1110" t="s">
-        <v>1136</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1111" t="s">
-        <v>1006</v>
-      </c>
-      <c r="B1111">
-        <v>20</v>
+        <v>641</v>
+      </c>
+      <c r="B1111" t="s">
+        <v>640</v>
       </c>
       <c r="C1111" t="s">
-        <v>1137</v>
+        <v>639</v>
       </c>
     </row>
     <row r="1112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1112" t="s">
-        <v>1007</v>
-      </c>
-      <c r="B1112">
-        <v>30</v>
+        <v>644</v>
+      </c>
+      <c r="B1112" t="s">
+        <v>643</v>
       </c>
       <c r="C1112" t="s">
-        <v>1138</v>
+        <v>642</v>
       </c>
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1113" t="s">
-        <v>1008</v>
-      </c>
-      <c r="B1113">
-        <v>40</v>
+        <v>647</v>
+      </c>
+      <c r="B1113" t="s">
+        <v>646</v>
       </c>
       <c r="C1113" t="s">
-        <v>1139</v>
+        <v>645</v>
       </c>
     </row>
     <row r="1114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1114" t="s">
-        <v>1009</v>
-      </c>
-      <c r="B1114">
-        <v>50</v>
+        <v>650</v>
+      </c>
+      <c r="B1114" t="s">
+        <v>649</v>
       </c>
       <c r="C1114" t="s">
-        <v>1140</v>
+        <v>648</v>
       </c>
     </row>
     <row r="1115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1115" t="s">
-        <v>1010</v>
-      </c>
-      <c r="B1115">
-        <v>60</v>
+        <v>651</v>
+      </c>
+      <c r="B1115" t="s">
+        <v>70</v>
       </c>
       <c r="C1115" t="s">
-        <v>1141</v>
+        <v>71</v>
       </c>
     </row>
     <row r="1116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1116" t="s">
-        <v>1011</v>
-      </c>
-      <c r="B1116">
-        <v>70</v>
+        <v>652</v>
+      </c>
+      <c r="B1116" t="s">
+        <v>84</v>
       </c>
       <c r="C1116" t="s">
-        <v>1142</v>
+        <v>85</v>
       </c>
     </row>
     <row r="1117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1117" t="s">
-        <v>1012</v>
-      </c>
-      <c r="B1117">
-        <v>80</v>
+        <v>653</v>
+      </c>
+      <c r="B1117" t="s">
+        <v>86</v>
       </c>
       <c r="C1117" t="s">
-        <v>1143</v>
+        <v>87</v>
       </c>
     </row>
     <row r="1118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1118" t="s">
-        <v>1013</v>
-      </c>
-      <c r="B1118">
-        <v>90</v>
+        <v>402</v>
+      </c>
+      <c r="B1118" t="s">
+        <v>403</v>
       </c>
       <c r="C1118" t="s">
-        <v>1144</v>
+        <v>403</v>
       </c>
     </row>
     <row r="1119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1119" t="s">
-        <v>429</v>
-      </c>
-      <c r="B1119">
-        <v>100</v>
+        <v>656</v>
+      </c>
+      <c r="B1119" t="s">
+        <v>655</v>
       </c>
       <c r="C1119" t="s">
-        <v>430</v>
+        <v>654</v>
       </c>
     </row>
     <row r="1120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1120" t="s">
-        <v>1014</v>
-      </c>
-      <c r="B1120">
-        <v>200</v>
+        <v>659</v>
+      </c>
+      <c r="B1120" t="s">
+        <v>658</v>
       </c>
       <c r="C1120" t="s">
-        <v>1145</v>
+        <v>657</v>
       </c>
     </row>
     <row r="1121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1121" t="s">
-        <v>1015</v>
-      </c>
-      <c r="B1121">
-        <v>300</v>
+        <v>660</v>
+      </c>
+      <c r="B1121" t="s">
+        <v>102</v>
       </c>
       <c r="C1121" t="s">
-        <v>1146</v>
+        <v>103</v>
       </c>
     </row>
     <row r="1122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1122" t="s">
-        <v>1016</v>
-      </c>
-      <c r="B1122">
-        <v>400</v>
+        <v>663</v>
+      </c>
+      <c r="B1122" t="s">
+        <v>662</v>
       </c>
       <c r="C1122" t="s">
-        <v>1147</v>
+        <v>661</v>
       </c>
     </row>
     <row r="1123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1123" t="s">
-        <v>1017</v>
-      </c>
-      <c r="B1123">
-        <v>500</v>
+        <v>665</v>
+      </c>
+      <c r="B1123" t="s">
+        <v>106</v>
       </c>
       <c r="C1123" t="s">
-        <v>1148</v>
+        <v>664</v>
       </c>
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1124" t="s">
-        <v>1018</v>
-      </c>
-      <c r="B1124">
-        <v>600</v>
+        <v>667</v>
+      </c>
+      <c r="B1124" t="s">
+        <v>666</v>
       </c>
       <c r="C1124" t="s">
-        <v>1149</v>
+        <v>109</v>
       </c>
     </row>
     <row r="1125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1125" t="s">
-        <v>1019</v>
-      </c>
-      <c r="B1125">
-        <v>700</v>
+        <v>670</v>
+      </c>
+      <c r="B1125" t="s">
+        <v>669</v>
       </c>
       <c r="C1125" t="s">
-        <v>1150</v>
+        <v>668</v>
       </c>
     </row>
     <row r="1126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1126" t="s">
-        <v>1020</v>
-      </c>
-      <c r="B1126">
-        <v>800</v>
-      </c>
-      <c r="C1126" t="s">
-        <v>1151</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1127" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B1127">
-        <v>900</v>
+        <v>674</v>
+      </c>
+      <c r="B1127" t="s">
+        <v>673</v>
       </c>
       <c r="C1127" t="s">
-        <v>1152</v>
+        <v>672</v>
       </c>
     </row>
     <row r="1128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1128" t="s">
-        <v>431</v>
-      </c>
-      <c r="B1128">
-        <v>1000</v>
+        <v>677</v>
+      </c>
+      <c r="B1128" t="s">
+        <v>676</v>
       </c>
       <c r="C1128" t="s">
-        <v>432</v>
+        <v>675</v>
       </c>
     </row>
     <row r="1129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1129" t="s">
-        <v>1022</v>
-      </c>
-      <c r="B1129">
-        <v>2000</v>
+        <v>680</v>
+      </c>
+      <c r="B1129" t="s">
+        <v>679</v>
       </c>
       <c r="C1129" t="s">
-        <v>1153</v>
+        <v>678</v>
       </c>
     </row>
     <row r="1130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1130" t="s">
-        <v>1023</v>
-      </c>
-      <c r="B1130">
-        <v>3000</v>
+        <v>683</v>
+      </c>
+      <c r="B1130" t="s">
+        <v>682</v>
       </c>
       <c r="C1130" t="s">
-        <v>1154</v>
+        <v>681</v>
       </c>
     </row>
     <row r="1131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1131" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B1131">
-        <v>4000</v>
+        <v>686</v>
+      </c>
+      <c r="B1131" t="s">
+        <v>685</v>
       </c>
       <c r="C1131" t="s">
-        <v>1155</v>
+        <v>684</v>
       </c>
     </row>
     <row r="1132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1132" t="s">
-        <v>1025</v>
-      </c>
-      <c r="B1132">
-        <v>5000</v>
+        <v>689</v>
+      </c>
+      <c r="B1132" t="s">
+        <v>688</v>
       </c>
       <c r="C1132" t="s">
-        <v>1156</v>
+        <v>687</v>
       </c>
     </row>
     <row r="1133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1133" t="s">
-        <v>1026</v>
-      </c>
-      <c r="B1133">
-        <v>6000</v>
+        <v>692</v>
+      </c>
+      <c r="B1133" t="s">
+        <v>691</v>
       </c>
       <c r="C1133" t="s">
-        <v>1157</v>
+        <v>690</v>
       </c>
     </row>
     <row r="1134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1134" t="s">
-        <v>1027</v>
-      </c>
-      <c r="B1134">
-        <v>7000</v>
+        <v>695</v>
+      </c>
+      <c r="B1134" t="s">
+        <v>694</v>
       </c>
       <c r="C1134" t="s">
-        <v>1158</v>
+        <v>693</v>
       </c>
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1135" t="s">
-        <v>1028</v>
-      </c>
-      <c r="B1135">
-        <v>8000</v>
+        <v>698</v>
+      </c>
+      <c r="B1135" t="s">
+        <v>697</v>
       </c>
       <c r="C1135" t="s">
-        <v>1159</v>
+        <v>696</v>
       </c>
     </row>
     <row r="1136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1136" t="s">
-        <v>1029</v>
-      </c>
-      <c r="B1136">
-        <v>9000</v>
+        <v>701</v>
+      </c>
+      <c r="B1136" t="s">
+        <v>700</v>
       </c>
       <c r="C1136" t="s">
-        <v>1160</v>
+        <v>699</v>
       </c>
     </row>
     <row r="1137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1137" t="s">
-        <v>1030</v>
+        <v>704</v>
       </c>
       <c r="B1137" t="s">
-        <v>1161</v>
+        <v>703</v>
       </c>
       <c r="C1137" t="s">
-        <v>435</v>
+        <v>702</v>
       </c>
     </row>
     <row r="1138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1138" t="s">
-        <v>1031</v>
-      </c>
-      <c r="B1138">
-        <v>20000</v>
+        <v>400</v>
+      </c>
+      <c r="B1138" t="s">
+        <v>706</v>
       </c>
       <c r="C1138" t="s">
-        <v>1162</v>
+        <v>705</v>
       </c>
     </row>
     <row r="1139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1139" t="s">
-        <v>1032</v>
-      </c>
-      <c r="B1139">
-        <v>30000</v>
+        <v>709</v>
+      </c>
+      <c r="B1139" t="s">
+        <v>708</v>
       </c>
       <c r="C1139" t="s">
-        <v>1163</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1140" t="s">
-        <v>1033</v>
-      </c>
-      <c r="B1140">
-        <v>40000</v>
+        <v>712</v>
+      </c>
+      <c r="B1140" t="s">
+        <v>711</v>
       </c>
       <c r="C1140" t="s">
-        <v>1164</v>
+        <v>710</v>
       </c>
     </row>
     <row r="1141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1141" t="s">
-        <v>1034</v>
-      </c>
-      <c r="B1141">
-        <v>50000</v>
+        <v>715</v>
+      </c>
+      <c r="B1141" t="s">
+        <v>714</v>
       </c>
       <c r="C1141" t="s">
-        <v>1165</v>
+        <v>713</v>
       </c>
     </row>
     <row r="1142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1142" t="s">
-        <v>1035</v>
-      </c>
-      <c r="B1142">
-        <v>60000</v>
+        <v>718</v>
+      </c>
+      <c r="B1142" t="s">
+        <v>717</v>
       </c>
       <c r="C1142" t="s">
-        <v>1166</v>
+        <v>716</v>
       </c>
     </row>
     <row r="1143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1143" t="s">
-        <v>1036</v>
-      </c>
-      <c r="B1143">
-        <v>70000</v>
-      </c>
-      <c r="C1143" t="s">
-        <v>1167</v>
+        <v>719</v>
       </c>
     </row>
     <row r="1144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1144" t="s">
-        <v>1037</v>
+        <v>720</v>
       </c>
       <c r="B1144">
-        <v>80000</v>
+        <v>1</v>
       </c>
       <c r="C1144" t="s">
-        <v>1168</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="1145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1145" t="s">
-        <v>1038</v>
+        <v>721</v>
       </c>
       <c r="B1145">
-        <v>90000</v>
+        <v>2</v>
       </c>
       <c r="C1145" t="s">
-        <v>1169</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1146" t="s">
-        <v>433</v>
-      </c>
-      <c r="B1146" t="s">
-        <v>434</v>
+        <v>722</v>
+      </c>
+      <c r="B1146">
+        <v>3</v>
       </c>
       <c r="C1146" t="s">
-        <v>435</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="1147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1147" t="s">
-        <v>1039</v>
-      </c>
-      <c r="B1147" t="s">
-        <v>1170</v>
+        <v>723</v>
+      </c>
+      <c r="B1147">
+        <v>4</v>
       </c>
       <c r="C1147" t="s">
-        <v>1170</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="1148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1148" t="s">
-        <v>1171</v>
-      </c>
-      <c r="B1148" t="s">
-        <v>1172</v>
+        <v>724</v>
+      </c>
+      <c r="B1148">
+        <v>5</v>
       </c>
       <c r="C1148" t="s">
-        <v>1172</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="1149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1149" t="s">
-        <v>1005</v>
+        <v>725</v>
+      </c>
+      <c r="B1149">
+        <v>6</v>
+      </c>
+      <c r="C1149" t="s">
+        <v>1132</v>
       </c>
     </row>
     <row r="1150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1150" t="s">
-        <v>732</v>
-      </c>
-      <c r="B1150" t="s">
-        <v>731</v>
+        <v>726</v>
+      </c>
+      <c r="B1150">
+        <v>7</v>
       </c>
       <c r="C1150" t="s">
-        <v>730</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="1151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1151" t="s">
-        <v>735</v>
-      </c>
-      <c r="B1151" t="s">
-        <v>734</v>
+        <v>727</v>
+      </c>
+      <c r="B1151">
+        <v>8</v>
       </c>
       <c r="C1151" t="s">
-        <v>733</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="1152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1152" t="s">
-        <v>738</v>
-      </c>
-      <c r="B1152" t="s">
-        <v>737</v>
+        <v>728</v>
+      </c>
+      <c r="B1152">
+        <v>9</v>
       </c>
       <c r="C1152" t="s">
-        <v>736</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="1153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1153" t="s">
-        <v>741</v>
-      </c>
-      <c r="B1153" t="s">
-        <v>740</v>
+        <v>729</v>
+      </c>
+      <c r="B1153">
+        <v>10</v>
       </c>
       <c r="C1153" t="s">
-        <v>739</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="1154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1154" t="s">
-        <v>744</v>
-      </c>
-      <c r="B1154" t="s">
-        <v>743</v>
+        <v>1006</v>
+      </c>
+      <c r="B1154">
+        <v>20</v>
       </c>
       <c r="C1154" t="s">
-        <v>742</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="1155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1155" t="s">
-        <v>747</v>
-      </c>
-      <c r="B1155" t="s">
-        <v>746</v>
+        <v>1007</v>
+      </c>
+      <c r="B1155">
+        <v>30</v>
       </c>
       <c r="C1155" t="s">
-        <v>745</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="1156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1156" t="s">
-        <v>750</v>
-      </c>
-      <c r="B1156" t="s">
-        <v>749</v>
+        <v>1008</v>
+      </c>
+      <c r="B1156">
+        <v>40</v>
       </c>
       <c r="C1156" t="s">
-        <v>748</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1157" t="s">
-        <v>753</v>
-      </c>
-      <c r="B1157" t="s">
-        <v>752</v>
+        <v>1009</v>
+      </c>
+      <c r="B1157">
+        <v>50</v>
       </c>
       <c r="C1157" t="s">
-        <v>751</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="1158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1158" t="s">
-        <v>756</v>
-      </c>
-      <c r="B1158" t="s">
-        <v>755</v>
+        <v>1010</v>
+      </c>
+      <c r="B1158">
+        <v>60</v>
       </c>
       <c r="C1158" t="s">
-        <v>754</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="1159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1159" t="s">
-        <v>759</v>
-      </c>
-      <c r="B1159" t="s">
-        <v>758</v>
+        <v>1011</v>
+      </c>
+      <c r="B1159">
+        <v>70</v>
       </c>
       <c r="C1159" t="s">
-        <v>757</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="1160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1160" t="s">
-        <v>762</v>
-      </c>
-      <c r="B1160" t="s">
-        <v>761</v>
+        <v>1012</v>
+      </c>
+      <c r="B1160">
+        <v>80</v>
       </c>
       <c r="C1160" t="s">
-        <v>760</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="1161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1161" t="s">
-        <v>765</v>
-      </c>
-      <c r="B1161" t="s">
-        <v>764</v>
+        <v>1013</v>
+      </c>
+      <c r="B1161">
+        <v>90</v>
       </c>
       <c r="C1161" t="s">
-        <v>763</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="1162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1162" t="s">
-        <v>768</v>
-      </c>
-      <c r="B1162" t="s">
-        <v>767</v>
+        <v>429</v>
+      </c>
+      <c r="B1162">
+        <v>100</v>
       </c>
       <c r="C1162" t="s">
-        <v>766</v>
+        <v>430</v>
       </c>
     </row>
     <row r="1163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1163" t="s">
-        <v>771</v>
-      </c>
-      <c r="B1163" t="s">
-        <v>770</v>
+        <v>1014</v>
+      </c>
+      <c r="B1163">
+        <v>200</v>
       </c>
       <c r="C1163" t="s">
-        <v>769</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="1164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1164" t="s">
-        <v>774</v>
-      </c>
-      <c r="B1164" t="s">
-        <v>773</v>
+        <v>1015</v>
+      </c>
+      <c r="B1164">
+        <v>300</v>
       </c>
       <c r="C1164" t="s">
-        <v>772</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="1165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1165" t="s">
-        <v>776</v>
-      </c>
-      <c r="B1165" t="s">
-        <v>775</v>
+        <v>1016</v>
+      </c>
+      <c r="B1165">
+        <v>400</v>
       </c>
       <c r="C1165" t="s">
-        <v>301</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="1166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1166" t="s">
-        <v>779</v>
-      </c>
-      <c r="B1166" t="s">
-        <v>778</v>
+        <v>1017</v>
+      </c>
+      <c r="B1166">
+        <v>500</v>
       </c>
       <c r="C1166" t="s">
-        <v>777</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="1167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1167" t="s">
-        <v>782</v>
-      </c>
-      <c r="B1167" t="s">
-        <v>781</v>
+        <v>1018</v>
+      </c>
+      <c r="B1167">
+        <v>600</v>
       </c>
       <c r="C1167" t="s">
-        <v>780</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1168" t="s">
-        <v>785</v>
-      </c>
-      <c r="B1168" t="s">
-        <v>784</v>
+        <v>1019</v>
+      </c>
+      <c r="B1168">
+        <v>700</v>
       </c>
       <c r="C1168" t="s">
-        <v>783</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="1169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1169" t="s">
-        <v>788</v>
-      </c>
-      <c r="B1169" t="s">
-        <v>787</v>
+        <v>1020</v>
+      </c>
+      <c r="B1169">
+        <v>800</v>
       </c>
       <c r="C1169" t="s">
-        <v>786</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="1170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1170" t="s">
-        <v>791</v>
-      </c>
-      <c r="B1170" t="s">
-        <v>790</v>
+        <v>1021</v>
+      </c>
+      <c r="B1170">
+        <v>900</v>
       </c>
       <c r="C1170" t="s">
-        <v>789</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="1171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1171" t="s">
-        <v>794</v>
-      </c>
-      <c r="B1171" t="s">
-        <v>793</v>
+        <v>431</v>
+      </c>
+      <c r="B1171">
+        <v>1000</v>
       </c>
       <c r="C1171" t="s">
-        <v>792</v>
+        <v>432</v>
       </c>
     </row>
     <row r="1172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1172" t="s">
-        <v>797</v>
-      </c>
-      <c r="B1172" t="s">
-        <v>796</v>
+        <v>1022</v>
+      </c>
+      <c r="B1172">
+        <v>2000</v>
       </c>
       <c r="C1172" t="s">
-        <v>795</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="1173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1173" t="s">
-        <v>800</v>
-      </c>
-      <c r="B1173" t="s">
-        <v>799</v>
+        <v>1023</v>
+      </c>
+      <c r="B1173">
+        <v>3000</v>
       </c>
       <c r="C1173" t="s">
-        <v>798</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="1174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1174" t="s">
-        <v>803</v>
-      </c>
-      <c r="B1174" t="s">
-        <v>802</v>
+        <v>1024</v>
+      </c>
+      <c r="B1174">
+        <v>4000</v>
       </c>
       <c r="C1174" t="s">
-        <v>801</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="1175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1175" t="s">
-        <v>806</v>
-      </c>
-      <c r="B1175" t="s">
-        <v>805</v>
+        <v>1025</v>
+      </c>
+      <c r="B1175">
+        <v>5000</v>
       </c>
       <c r="C1175" t="s">
-        <v>804</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="1176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1176" t="s">
-        <v>809</v>
-      </c>
-      <c r="B1176" t="s">
-        <v>808</v>
+        <v>1026</v>
+      </c>
+      <c r="B1176">
+        <v>6000</v>
       </c>
       <c r="C1176" t="s">
-        <v>807</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="1177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1177" t="s">
-        <v>812</v>
-      </c>
-      <c r="B1177" t="s">
-        <v>811</v>
+        <v>1027</v>
+      </c>
+      <c r="B1177">
+        <v>7000</v>
       </c>
       <c r="C1177" t="s">
-        <v>810</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="1178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1178" t="s">
-        <v>815</v>
-      </c>
-      <c r="B1178" t="s">
-        <v>814</v>
+        <v>1028</v>
+      </c>
+      <c r="B1178">
+        <v>8000</v>
       </c>
       <c r="C1178" t="s">
-        <v>813</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1179" t="s">
-        <v>818</v>
-      </c>
-      <c r="B1179" t="s">
-        <v>817</v>
+        <v>1029</v>
+      </c>
+      <c r="B1179">
+        <v>9000</v>
       </c>
       <c r="C1179" t="s">
-        <v>816</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="1180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1180" t="s">
-        <v>821</v>
+        <v>1030</v>
       </c>
       <c r="B1180" t="s">
-        <v>820</v>
+        <v>1161</v>
       </c>
       <c r="C1180" t="s">
-        <v>819</v>
+        <v>435</v>
       </c>
     </row>
     <row r="1181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1181" t="s">
-        <v>824</v>
-      </c>
-      <c r="B1181" t="s">
-        <v>823</v>
+        <v>1031</v>
+      </c>
+      <c r="B1181">
+        <v>20000</v>
       </c>
       <c r="C1181" t="s">
-        <v>822</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="1182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1182" t="s">
-        <v>827</v>
-      </c>
-      <c r="B1182" t="s">
-        <v>826</v>
+        <v>1032</v>
+      </c>
+      <c r="B1182">
+        <v>30000</v>
       </c>
       <c r="C1182" t="s">
-        <v>825</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="1183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1183" t="s">
-        <v>830</v>
-      </c>
-      <c r="B1183" t="s">
-        <v>829</v>
+        <v>1033</v>
+      </c>
+      <c r="B1183">
+        <v>40000</v>
       </c>
       <c r="C1183" t="s">
-        <v>828</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="1184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1184" t="s">
-        <v>833</v>
-      </c>
-      <c r="B1184" t="s">
-        <v>832</v>
+        <v>1034</v>
+      </c>
+      <c r="B1184">
+        <v>50000</v>
       </c>
       <c r="C1184" t="s">
-        <v>831</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="1185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1185" t="s">
-        <v>836</v>
-      </c>
-      <c r="B1185" t="s">
-        <v>835</v>
+        <v>1035</v>
+      </c>
+      <c r="B1185">
+        <v>60000</v>
       </c>
       <c r="C1185" t="s">
-        <v>834</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="1186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1186" t="s">
-        <v>839</v>
-      </c>
-      <c r="B1186" t="s">
-        <v>838</v>
+        <v>1036</v>
+      </c>
+      <c r="B1186">
+        <v>70000</v>
       </c>
       <c r="C1186" t="s">
-        <v>837</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="1187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1187" t="s">
-        <v>842</v>
-      </c>
-      <c r="B1187" t="s">
-        <v>841</v>
+        <v>1037</v>
+      </c>
+      <c r="B1187">
+        <v>80000</v>
       </c>
       <c r="C1187" t="s">
-        <v>840</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="1188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1188" t="s">
-        <v>845</v>
-      </c>
-      <c r="B1188" t="s">
-        <v>844</v>
+        <v>1038</v>
+      </c>
+      <c r="B1188">
+        <v>90000</v>
       </c>
       <c r="C1188" t="s">
-        <v>843</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="1189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1189" t="s">
-        <v>848</v>
+        <v>433</v>
       </c>
       <c r="B1189" t="s">
-        <v>847</v>
+        <v>434</v>
       </c>
       <c r="C1189" t="s">
-        <v>846</v>
+        <v>435</v>
       </c>
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1190" t="s">
-        <v>851</v>
+        <v>1039</v>
       </c>
       <c r="B1190" t="s">
-        <v>850</v>
+        <v>1170</v>
       </c>
       <c r="C1190" t="s">
-        <v>849</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="1191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1191" t="s">
-        <v>854</v>
+        <v>1171</v>
       </c>
       <c r="B1191" t="s">
-        <v>853</v>
+        <v>1172</v>
       </c>
       <c r="C1191" t="s">
-        <v>852</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="1192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1192" t="s">
-        <v>855</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="1193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1193" t="s">
-        <v>858</v>
+        <v>732</v>
       </c>
       <c r="B1193" t="s">
-        <v>857</v>
+        <v>731</v>
       </c>
       <c r="C1193" t="s">
-        <v>856</v>
+        <v>730</v>
       </c>
     </row>
     <row r="1194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1194" t="s">
-        <v>861</v>
+        <v>735</v>
       </c>
       <c r="B1194" t="s">
-        <v>860</v>
+        <v>734</v>
       </c>
       <c r="C1194" t="s">
-        <v>859</v>
+        <v>733</v>
       </c>
     </row>
     <row r="1195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1195" t="s">
-        <v>864</v>
+        <v>738</v>
       </c>
       <c r="B1195" t="s">
-        <v>863</v>
+        <v>737</v>
       </c>
       <c r="C1195" t="s">
-        <v>862</v>
+        <v>736</v>
       </c>
     </row>
     <row r="1196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1196" t="s">
-        <v>867</v>
+        <v>741</v>
       </c>
       <c r="B1196" t="s">
-        <v>866</v>
+        <v>740</v>
       </c>
       <c r="C1196" t="s">
-        <v>865</v>
+        <v>739</v>
       </c>
     </row>
     <row r="1197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1197" t="s">
-        <v>870</v>
+        <v>744</v>
       </c>
       <c r="B1197" t="s">
-        <v>869</v>
+        <v>743</v>
       </c>
       <c r="C1197" t="s">
-        <v>868</v>
+        <v>742</v>
       </c>
     </row>
     <row r="1198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1198" t="s">
-        <v>858</v>
+        <v>747</v>
       </c>
       <c r="B1198" t="s">
-        <v>872</v>
+        <v>746</v>
       </c>
       <c r="C1198" t="s">
-        <v>871</v>
+        <v>745</v>
       </c>
     </row>
     <row r="1199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1199" t="s">
-        <v>875</v>
+        <v>750</v>
       </c>
       <c r="B1199" t="s">
-        <v>874</v>
+        <v>749</v>
       </c>
       <c r="C1199" t="s">
-        <v>873</v>
+        <v>748</v>
       </c>
     </row>
     <row r="1200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1200" t="s">
-        <v>878</v>
+        <v>753</v>
       </c>
       <c r="B1200" t="s">
-        <v>877</v>
+        <v>752</v>
       </c>
       <c r="C1200" t="s">
-        <v>876</v>
+        <v>751</v>
       </c>
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1201" t="s">
-        <v>881</v>
+        <v>756</v>
       </c>
       <c r="B1201" t="s">
-        <v>880</v>
+        <v>755</v>
       </c>
       <c r="C1201" t="s">
-        <v>879</v>
+        <v>754</v>
       </c>
     </row>
     <row r="1202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1202" t="s">
-        <v>884</v>
+        <v>759</v>
       </c>
       <c r="B1202" t="s">
-        <v>883</v>
+        <v>758</v>
       </c>
       <c r="C1202" t="s">
-        <v>882</v>
+        <v>757</v>
       </c>
     </row>
     <row r="1203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1203" t="s">
-        <v>887</v>
+        <v>762</v>
       </c>
       <c r="B1203" t="s">
-        <v>886</v>
+        <v>761</v>
       </c>
       <c r="C1203" t="s">
-        <v>885</v>
+        <v>760</v>
       </c>
     </row>
     <row r="1204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1204" t="s">
-        <v>890</v>
+        <v>765</v>
       </c>
       <c r="B1204" t="s">
-        <v>889</v>
+        <v>764</v>
       </c>
       <c r="C1204" t="s">
-        <v>888</v>
+        <v>763</v>
       </c>
     </row>
     <row r="1205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1205" t="s">
-        <v>893</v>
+        <v>768</v>
       </c>
       <c r="B1205" t="s">
-        <v>892</v>
+        <v>767</v>
       </c>
       <c r="C1205" t="s">
-        <v>891</v>
+        <v>766</v>
       </c>
     </row>
     <row r="1206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1206" t="s">
-        <v>896</v>
+        <v>771</v>
       </c>
       <c r="B1206" t="s">
-        <v>895</v>
+        <v>770</v>
       </c>
       <c r="C1206" t="s">
-        <v>894</v>
+        <v>769</v>
       </c>
     </row>
     <row r="1207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1207" t="s">
-        <v>899</v>
+        <v>774</v>
       </c>
       <c r="B1207" t="s">
-        <v>898</v>
+        <v>773</v>
       </c>
       <c r="C1207" t="s">
-        <v>897</v>
+        <v>772</v>
       </c>
     </row>
     <row r="1208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1208" t="s">
-        <v>902</v>
+        <v>776</v>
       </c>
       <c r="B1208" t="s">
-        <v>901</v>
+        <v>775</v>
       </c>
       <c r="C1208" t="s">
-        <v>900</v>
+        <v>301</v>
       </c>
     </row>
     <row r="1209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1209" t="s">
-        <v>902</v>
+        <v>779</v>
       </c>
       <c r="B1209" t="s">
-        <v>904</v>
+        <v>778</v>
       </c>
       <c r="C1209" t="s">
-        <v>903</v>
+        <v>777</v>
       </c>
     </row>
     <row r="1210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1210" t="s">
-        <v>907</v>
+        <v>782</v>
       </c>
       <c r="B1210" t="s">
-        <v>906</v>
+        <v>781</v>
       </c>
       <c r="C1210" t="s">
-        <v>905</v>
+        <v>780</v>
       </c>
     </row>
     <row r="1211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1211" t="s">
-        <v>910</v>
+        <v>785</v>
       </c>
       <c r="B1211" t="s">
-        <v>909</v>
+        <v>784</v>
       </c>
       <c r="C1211" t="s">
-        <v>908</v>
+        <v>783</v>
       </c>
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1212" t="s">
-        <v>913</v>
+        <v>788</v>
       </c>
       <c r="B1212" t="s">
-        <v>912</v>
+        <v>787</v>
       </c>
       <c r="C1212" t="s">
-        <v>911</v>
+        <v>786</v>
       </c>
     </row>
     <row r="1213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1213" t="s">
-        <v>916</v>
+        <v>791</v>
       </c>
       <c r="B1213" t="s">
-        <v>915</v>
+        <v>790</v>
       </c>
       <c r="C1213" t="s">
-        <v>914</v>
+        <v>789</v>
       </c>
     </row>
     <row r="1214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1214" t="s">
-        <v>919</v>
+        <v>794</v>
       </c>
       <c r="B1214" t="s">
-        <v>918</v>
+        <v>793</v>
       </c>
       <c r="C1214" t="s">
-        <v>917</v>
+        <v>792</v>
       </c>
     </row>
     <row r="1215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1215" t="s">
-        <v>922</v>
+        <v>797</v>
       </c>
       <c r="B1215" t="s">
-        <v>921</v>
+        <v>796</v>
       </c>
       <c r="C1215" t="s">
-        <v>920</v>
+        <v>795</v>
       </c>
     </row>
     <row r="1216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1216" t="s">
-        <v>925</v>
+        <v>800</v>
       </c>
       <c r="B1216" t="s">
-        <v>924</v>
+        <v>799</v>
       </c>
       <c r="C1216" t="s">
-        <v>923</v>
+        <v>798</v>
       </c>
     </row>
     <row r="1217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1217" t="s">
-        <v>928</v>
+        <v>803</v>
       </c>
       <c r="B1217" t="s">
-        <v>927</v>
+        <v>802</v>
       </c>
       <c r="C1217" t="s">
-        <v>926</v>
+        <v>801</v>
       </c>
     </row>
     <row r="1218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1218" t="s">
-        <v>931</v>
+        <v>806</v>
       </c>
       <c r="B1218" t="s">
-        <v>930</v>
+        <v>805</v>
       </c>
       <c r="C1218" t="s">
-        <v>929</v>
+        <v>804</v>
       </c>
     </row>
     <row r="1219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1219" t="s">
-        <v>934</v>
+        <v>809</v>
       </c>
       <c r="B1219" t="s">
-        <v>933</v>
+        <v>808</v>
       </c>
       <c r="C1219" t="s">
-        <v>932</v>
+        <v>807</v>
       </c>
     </row>
     <row r="1220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1220" t="s">
-        <v>937</v>
+        <v>812</v>
       </c>
       <c r="B1220" t="s">
-        <v>936</v>
+        <v>811</v>
       </c>
       <c r="C1220" t="s">
-        <v>935</v>
+        <v>810</v>
       </c>
     </row>
     <row r="1221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1221" t="s">
-        <v>940</v>
+        <v>815</v>
       </c>
       <c r="B1221" t="s">
-        <v>939</v>
+        <v>814</v>
       </c>
       <c r="C1221" t="s">
-        <v>938</v>
+        <v>813</v>
       </c>
     </row>
     <row r="1222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1222" t="s">
-        <v>943</v>
+        <v>818</v>
       </c>
       <c r="B1222" t="s">
-        <v>942</v>
+        <v>817</v>
       </c>
       <c r="C1222" t="s">
-        <v>941</v>
+        <v>816</v>
       </c>
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1223" t="s">
-        <v>946</v>
+        <v>821</v>
       </c>
       <c r="B1223" t="s">
-        <v>945</v>
+        <v>820</v>
       </c>
       <c r="C1223" t="s">
-        <v>944</v>
+        <v>819</v>
       </c>
     </row>
     <row r="1224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1224" t="s">
-        <v>948</v>
+        <v>824</v>
       </c>
       <c r="B1224" t="s">
-        <v>948</v>
+        <v>823</v>
       </c>
       <c r="C1224" t="s">
-        <v>947</v>
+        <v>822</v>
       </c>
     </row>
     <row r="1225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1225" t="s">
-        <v>951</v>
+        <v>827</v>
       </c>
       <c r="B1225" t="s">
-        <v>950</v>
+        <v>826</v>
       </c>
       <c r="C1225" t="s">
-        <v>949</v>
+        <v>825</v>
       </c>
     </row>
     <row r="1226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1226" t="s">
-        <v>954</v>
+        <v>830</v>
       </c>
       <c r="B1226" t="s">
-        <v>953</v>
+        <v>829</v>
       </c>
       <c r="C1226" t="s">
-        <v>952</v>
+        <v>828</v>
       </c>
     </row>
     <row r="1227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1227" t="s">
-        <v>957</v>
+        <v>833</v>
       </c>
       <c r="B1227" t="s">
-        <v>956</v>
+        <v>832</v>
       </c>
       <c r="C1227" t="s">
-        <v>955</v>
+        <v>831</v>
       </c>
     </row>
     <row r="1228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1228" t="s">
-        <v>960</v>
+        <v>836</v>
       </c>
       <c r="B1228" t="s">
-        <v>959</v>
+        <v>835</v>
       </c>
       <c r="C1228" t="s">
-        <v>958</v>
+        <v>834</v>
       </c>
     </row>
     <row r="1229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1229" t="s">
-        <v>962</v>
+        <v>839</v>
+      </c>
+      <c r="B1229" t="s">
+        <v>838</v>
       </c>
       <c r="C1229" t="s">
-        <v>961</v>
+        <v>837</v>
       </c>
     </row>
     <row r="1230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1230" t="s">
-        <v>965</v>
+        <v>842</v>
       </c>
       <c r="B1230" t="s">
-        <v>964</v>
+        <v>841</v>
       </c>
       <c r="C1230" t="s">
-        <v>963</v>
+        <v>840</v>
       </c>
     </row>
     <row r="1231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1231" t="s">
-        <v>968</v>
+        <v>845</v>
       </c>
       <c r="B1231" t="s">
-        <v>967</v>
+        <v>844</v>
       </c>
       <c r="C1231" t="s">
-        <v>966</v>
+        <v>843</v>
       </c>
     </row>
     <row r="1232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1232" t="s">
-        <v>965</v>
+        <v>848</v>
       </c>
       <c r="B1232" t="s">
-        <v>970</v>
+        <v>847</v>
       </c>
       <c r="C1232" t="s">
-        <v>969</v>
+        <v>846</v>
       </c>
     </row>
     <row r="1233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1233" t="s">
-        <v>973</v>
+        <v>851</v>
       </c>
       <c r="B1233" t="s">
-        <v>972</v>
+        <v>850</v>
       </c>
       <c r="C1233" t="s">
-        <v>971</v>
+        <v>849</v>
       </c>
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1234" t="s">
-        <v>976</v>
+        <v>854</v>
       </c>
       <c r="B1234" t="s">
-        <v>975</v>
+        <v>853</v>
       </c>
       <c r="C1234" t="s">
-        <v>974</v>
+        <v>852</v>
       </c>
     </row>
     <row r="1235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1235" t="s">
-        <v>979</v>
-      </c>
-      <c r="B1235" t="s">
-        <v>978</v>
-      </c>
-      <c r="C1235" t="s">
-        <v>977</v>
+        <v>855</v>
       </c>
     </row>
     <row r="1236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1236" t="s">
-        <v>982</v>
+        <v>858</v>
       </c>
       <c r="B1236" t="s">
-        <v>981</v>
+        <v>857</v>
       </c>
       <c r="C1236" t="s">
-        <v>980</v>
+        <v>856</v>
       </c>
     </row>
     <row r="1237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1237" t="s">
-        <v>985</v>
+        <v>861</v>
       </c>
       <c r="B1237" t="s">
-        <v>984</v>
+        <v>860</v>
       </c>
       <c r="C1237" t="s">
-        <v>983</v>
+        <v>859</v>
       </c>
     </row>
     <row r="1238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1238" t="s">
-        <v>988</v>
+        <v>864</v>
       </c>
       <c r="B1238" t="s">
-        <v>987</v>
+        <v>863</v>
       </c>
       <c r="C1238" t="s">
-        <v>986</v>
+        <v>862</v>
       </c>
     </row>
     <row r="1239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1239" t="s">
-        <v>990</v>
+        <v>867</v>
+      </c>
+      <c r="B1239" t="s">
+        <v>866</v>
       </c>
       <c r="C1239" t="s">
-        <v>989</v>
+        <v>865</v>
       </c>
     </row>
     <row r="1240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1240" t="s">
-        <v>993</v>
+        <v>870</v>
       </c>
       <c r="B1240" t="s">
-        <v>992</v>
+        <v>869</v>
       </c>
       <c r="C1240" t="s">
-        <v>991</v>
+        <v>868</v>
       </c>
     </row>
     <row r="1241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1241" t="s">
-        <v>996</v>
+        <v>858</v>
       </c>
       <c r="B1241" t="s">
-        <v>995</v>
+        <v>872</v>
       </c>
       <c r="C1241" t="s">
-        <v>994</v>
+        <v>871</v>
       </c>
     </row>
     <row r="1242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1242" t="s">
-        <v>998</v>
+        <v>875</v>
       </c>
       <c r="B1242" t="s">
-        <v>997</v>
+        <v>874</v>
       </c>
       <c r="C1242" t="s">
-        <v>997</v>
+        <v>873</v>
       </c>
     </row>
     <row r="1243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1243" t="s">
-        <v>1001</v>
+        <v>878</v>
       </c>
       <c r="B1243" t="s">
-        <v>1000</v>
+        <v>877</v>
       </c>
       <c r="C1243" t="s">
-        <v>999</v>
+        <v>876</v>
       </c>
     </row>
     <row r="1244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1244" t="s">
-        <v>1004</v>
+        <v>881</v>
       </c>
       <c r="B1244" t="s">
-        <v>1003</v>
+        <v>880</v>
       </c>
       <c r="C1244" t="s">
-        <v>1002</v>
+        <v>879</v>
       </c>
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1245" t="s">
-        <v>1173</v>
+        <v>884</v>
+      </c>
+      <c r="B1245" t="s">
+        <v>883</v>
+      </c>
+      <c r="C1245" t="s">
+        <v>882</v>
       </c>
     </row>
     <row r="1246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1246" t="s">
-        <v>1040</v>
+        <v>887</v>
       </c>
       <c r="B1246" t="s">
-        <v>1041</v>
+        <v>886</v>
       </c>
       <c r="C1246" t="s">
-        <v>1042</v>
+        <v>885</v>
       </c>
     </row>
     <row r="1247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1247" t="s">
-        <v>1043</v>
+        <v>890</v>
       </c>
       <c r="B1247" t="s">
-        <v>1044</v>
+        <v>889</v>
       </c>
       <c r="C1247" t="s">
-        <v>1045</v>
+        <v>888</v>
       </c>
     </row>
     <row r="1248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1248" t="s">
-        <v>1046</v>
+        <v>893</v>
       </c>
       <c r="B1248" t="s">
-        <v>1047</v>
+        <v>892</v>
       </c>
       <c r="C1248" t="s">
-        <v>1048</v>
+        <v>891</v>
       </c>
     </row>
     <row r="1249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1249" t="s">
-        <v>1049</v>
+        <v>896</v>
       </c>
       <c r="B1249" t="s">
-        <v>1050</v>
+        <v>895</v>
       </c>
       <c r="C1249" t="s">
-        <v>1051</v>
+        <v>894</v>
       </c>
     </row>
     <row r="1250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1250" t="s">
-        <v>1052</v>
+        <v>899</v>
       </c>
       <c r="B1250" t="s">
-        <v>1053</v>
+        <v>898</v>
       </c>
       <c r="C1250" t="s">
-        <v>1054</v>
+        <v>897</v>
       </c>
     </row>
     <row r="1251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1251" t="s">
-        <v>1055</v>
+        <v>902</v>
       </c>
       <c r="B1251" t="s">
-        <v>1056</v>
+        <v>901</v>
       </c>
       <c r="C1251" t="s">
-        <v>1057</v>
+        <v>900</v>
       </c>
     </row>
     <row r="1252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1252" t="s">
-        <v>1058</v>
+        <v>902</v>
       </c>
       <c r="B1252" t="s">
-        <v>1059</v>
+        <v>904</v>
       </c>
       <c r="C1252" t="s">
-        <v>1060</v>
+        <v>903</v>
       </c>
     </row>
     <row r="1253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1253" t="s">
-        <v>1061</v>
+        <v>907</v>
       </c>
       <c r="B1253" t="s">
-        <v>1062</v>
+        <v>906</v>
       </c>
       <c r="C1253" t="s">
-        <v>1062</v>
+        <v>905</v>
       </c>
     </row>
     <row r="1254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1254" t="s">
-        <v>1063</v>
+        <v>910</v>
       </c>
       <c r="B1254" t="s">
-        <v>1064</v>
+        <v>909</v>
       </c>
       <c r="C1254" t="s">
-        <v>1064</v>
+        <v>908</v>
       </c>
     </row>
     <row r="1255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1255" t="s">
-        <v>1065</v>
+        <v>913</v>
       </c>
       <c r="B1255" t="s">
-        <v>1066</v>
+        <v>912</v>
       </c>
       <c r="C1255" t="s">
-        <v>1066</v>
+        <v>911</v>
       </c>
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1256" t="s">
-        <v>1067</v>
+        <v>916</v>
       </c>
       <c r="B1256" t="s">
-        <v>1068</v>
+        <v>915</v>
       </c>
       <c r="C1256" t="s">
-        <v>1068</v>
+        <v>914</v>
       </c>
     </row>
     <row r="1257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1257" t="s">
-        <v>1069</v>
+        <v>919</v>
       </c>
       <c r="B1257" t="s">
-        <v>1070</v>
+        <v>918</v>
       </c>
       <c r="C1257" t="s">
-        <v>1070</v>
+        <v>917</v>
       </c>
     </row>
     <row r="1258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1258" t="s">
-        <v>1071</v>
+        <v>922</v>
       </c>
       <c r="B1258" t="s">
-        <v>1072</v>
+        <v>921</v>
       </c>
       <c r="C1258" t="s">
-        <v>1072</v>
+        <v>920</v>
       </c>
     </row>
     <row r="1259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1259" t="s">
-        <v>1073</v>
+        <v>925</v>
       </c>
       <c r="B1259" t="s">
-        <v>1074</v>
+        <v>924</v>
       </c>
       <c r="C1259" t="s">
-        <v>1074</v>
+        <v>923</v>
       </c>
     </row>
     <row r="1260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1260" t="s">
-        <v>1075</v>
+        <v>928</v>
       </c>
       <c r="B1260" t="s">
-        <v>1076</v>
+        <v>927</v>
       </c>
       <c r="C1260" t="s">
-        <v>1076</v>
+        <v>926</v>
       </c>
     </row>
     <row r="1261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1261" t="s">
-        <v>1077</v>
+        <v>931</v>
       </c>
       <c r="B1261" t="s">
-        <v>1078</v>
+        <v>930</v>
       </c>
       <c r="C1261" t="s">
-        <v>1078</v>
+        <v>929</v>
       </c>
     </row>
     <row r="1262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1262" t="s">
-        <v>1079</v>
+        <v>934</v>
       </c>
       <c r="B1262" t="s">
-        <v>1080</v>
+        <v>933</v>
       </c>
       <c r="C1262" t="s">
-        <v>1080</v>
+        <v>932</v>
       </c>
     </row>
     <row r="1263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1263" t="s">
-        <v>1081</v>
+        <v>937</v>
       </c>
       <c r="B1263" t="s">
-        <v>1082</v>
+        <v>936</v>
       </c>
       <c r="C1263" t="s">
-        <v>1082</v>
+        <v>935</v>
       </c>
     </row>
     <row r="1264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1264" t="s">
-        <v>1083</v>
+        <v>940</v>
       </c>
       <c r="B1264" t="s">
-        <v>1084</v>
+        <v>939</v>
       </c>
       <c r="C1264" t="s">
-        <v>1084</v>
+        <v>938</v>
       </c>
     </row>
     <row r="1265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1265" t="s">
-        <v>1085</v>
+        <v>943</v>
       </c>
       <c r="B1265" t="s">
-        <v>1086</v>
+        <v>942</v>
       </c>
       <c r="C1265" t="s">
-        <v>1086</v>
+        <v>941</v>
       </c>
     </row>
     <row r="1266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1266" t="s">
-        <v>1087</v>
+        <v>946</v>
       </c>
       <c r="B1266" t="s">
-        <v>1088</v>
+        <v>945</v>
       </c>
       <c r="C1266" t="s">
-        <v>1088</v>
+        <v>944</v>
       </c>
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1267" t="s">
-        <v>1089</v>
+        <v>948</v>
       </c>
       <c r="B1267" t="s">
-        <v>1090</v>
+        <v>948</v>
       </c>
       <c r="C1267" t="s">
-        <v>1090</v>
+        <v>947</v>
       </c>
     </row>
     <row r="1268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1268" t="s">
-        <v>1091</v>
+        <v>951</v>
       </c>
       <c r="B1268" t="s">
-        <v>1092</v>
+        <v>950</v>
       </c>
       <c r="C1268" t="s">
-        <v>1092</v>
+        <v>949</v>
       </c>
     </row>
     <row r="1269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1269" t="s">
-        <v>1093</v>
+        <v>954</v>
       </c>
       <c r="B1269" t="s">
-        <v>1094</v>
+        <v>953</v>
       </c>
       <c r="C1269" t="s">
-        <v>1094</v>
+        <v>952</v>
       </c>
     </row>
     <row r="1270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1270" t="s">
-        <v>1095</v>
+        <v>957</v>
       </c>
       <c r="B1270" t="s">
-        <v>1096</v>
+        <v>956</v>
       </c>
       <c r="C1270" t="s">
-        <v>1096</v>
+        <v>955</v>
       </c>
     </row>
     <row r="1271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1271" t="s">
-        <v>1097</v>
+        <v>960</v>
       </c>
       <c r="B1271" t="s">
-        <v>1098</v>
+        <v>959</v>
       </c>
       <c r="C1271" t="s">
-        <v>1098</v>
+        <v>958</v>
       </c>
     </row>
     <row r="1272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1272" t="s">
-        <v>1099</v>
-      </c>
-      <c r="B1272" t="s">
-        <v>1100</v>
+        <v>962</v>
       </c>
       <c r="C1272" t="s">
-        <v>1101</v>
+        <v>961</v>
       </c>
     </row>
     <row r="1273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1273" t="s">
-        <v>1102</v>
+        <v>965</v>
       </c>
       <c r="B1273" t="s">
-        <v>1103</v>
+        <v>964</v>
       </c>
       <c r="C1273" t="s">
-        <v>1104</v>
+        <v>963</v>
       </c>
     </row>
     <row r="1274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1274" t="s">
-        <v>1105</v>
+        <v>968</v>
       </c>
       <c r="B1274" t="s">
-        <v>1106</v>
+        <v>967</v>
       </c>
       <c r="C1274" t="s">
-        <v>1107</v>
+        <v>966</v>
       </c>
     </row>
     <row r="1275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1275" t="s">
-        <v>1108</v>
+        <v>965</v>
       </c>
       <c r="B1275" t="s">
-        <v>1109</v>
+        <v>970</v>
       </c>
       <c r="C1275" t="s">
-        <v>1110</v>
+        <v>969</v>
       </c>
     </row>
     <row r="1276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1276" t="s">
-        <v>1111</v>
+        <v>973</v>
       </c>
       <c r="B1276" t="s">
-        <v>1112</v>
+        <v>972</v>
       </c>
       <c r="C1276" t="s">
-        <v>1113</v>
+        <v>971</v>
       </c>
     </row>
     <row r="1277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1277" t="s">
-        <v>1114</v>
+        <v>976</v>
       </c>
       <c r="B1277" t="s">
-        <v>1115</v>
+        <v>975</v>
       </c>
       <c r="C1277" t="s">
-        <v>1116</v>
+        <v>974</v>
       </c>
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1278" t="s">
-        <v>1117</v>
+        <v>979</v>
       </c>
       <c r="B1278" t="s">
-        <v>1118</v>
+        <v>978</v>
       </c>
       <c r="C1278" t="s">
-        <v>1119</v>
+        <v>977</v>
       </c>
     </row>
     <row r="1279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1279" t="s">
-        <v>1120</v>
+        <v>982</v>
       </c>
       <c r="B1279" t="s">
-        <v>1121</v>
+        <v>981</v>
       </c>
       <c r="C1279" t="s">
-        <v>1122</v>
+        <v>980</v>
       </c>
     </row>
     <row r="1280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1280" t="s">
-        <v>1123</v>
+        <v>985</v>
       </c>
       <c r="B1280" t="s">
-        <v>1124</v>
+        <v>984</v>
       </c>
       <c r="C1280" t="s">
-        <v>1125</v>
+        <v>983</v>
       </c>
     </row>
     <row r="1281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1281" t="s">
-        <v>2124</v>
+        <v>988</v>
+      </c>
+      <c r="B1281" t="s">
+        <v>987</v>
+      </c>
+      <c r="C1281" t="s">
+        <v>986</v>
       </c>
     </row>
     <row r="1282" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1282" s="4" t="s">
-        <v>2116</v>
-      </c>
-      <c r="B1282" s="4" t="s">
-        <v>2125</v>
+      <c r="A1282" t="s">
+        <v>990</v>
+      </c>
+      <c r="C1282" t="s">
+        <v>989</v>
       </c>
     </row>
     <row r="1283" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1283" s="4" t="s">
-        <v>2117</v>
-      </c>
-      <c r="B1283" s="4" t="s">
-        <v>2126</v>
+      <c r="A1283" t="s">
+        <v>993</v>
+      </c>
+      <c r="B1283" t="s">
+        <v>992</v>
+      </c>
+      <c r="C1283" t="s">
+        <v>991</v>
       </c>
     </row>
     <row r="1284" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1284" s="4" t="s">
-        <v>2118</v>
-      </c>
-      <c r="B1284" s="4" t="s">
-        <v>2127</v>
+      <c r="A1284" t="s">
+        <v>996</v>
+      </c>
+      <c r="B1284" t="s">
+        <v>995</v>
+      </c>
+      <c r="C1284" t="s">
+        <v>994</v>
       </c>
     </row>
     <row r="1285" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1285" s="4" t="s">
-        <v>2119</v>
-      </c>
-      <c r="B1285" s="4" t="s">
-        <v>2128</v>
+      <c r="A1285" t="s">
+        <v>998</v>
+      </c>
+      <c r="B1285" t="s">
+        <v>997</v>
+      </c>
+      <c r="C1285" t="s">
+        <v>997</v>
       </c>
     </row>
     <row r="1286" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1286" s="5" t="s">
-        <v>2120</v>
-      </c>
-      <c r="B1286" s="5" t="s">
-        <v>2129</v>
+      <c r="A1286" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B1286" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C1286" t="s">
+        <v>999</v>
       </c>
     </row>
     <row r="1287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1287" t="s">
-        <v>2130</v>
+        <v>1004</v>
       </c>
       <c r="B1287" t="s">
-        <v>2131</v>
+        <v>1003</v>
       </c>
       <c r="C1287" t="s">
-        <v>730</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="1288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1288" t="s">
-        <v>2132</v>
-      </c>
-      <c r="B1288" t="s">
-        <v>2133</v>
-      </c>
-      <c r="C1288" t="s">
-        <v>849</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1289" t="s">
-        <v>2134</v>
+        <v>1040</v>
       </c>
       <c r="B1289" t="s">
-        <v>2135</v>
+        <v>1041</v>
       </c>
       <c r="C1289" t="s">
-        <v>2121</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="1290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1290" t="s">
-        <v>2136</v>
+        <v>1043</v>
       </c>
       <c r="B1290" t="s">
-        <v>2137</v>
+        <v>1044</v>
       </c>
       <c r="C1290" t="s">
-        <v>763</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="1291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1291" t="s">
-        <v>2138</v>
+        <v>1046</v>
       </c>
       <c r="B1291" t="s">
-        <v>2139</v>
+        <v>1047</v>
       </c>
       <c r="C1291" t="s">
-        <v>2122</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="1292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1292" t="s">
-        <v>2140</v>
+        <v>1049</v>
       </c>
       <c r="B1292" t="s">
-        <v>2141</v>
+        <v>1050</v>
       </c>
       <c r="C1292" t="s">
-        <v>852</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="1293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1293" t="s">
-        <v>2142</v>
+        <v>1052</v>
       </c>
       <c r="B1293" t="s">
-        <v>2143</v>
+        <v>1053</v>
       </c>
       <c r="C1293" t="s">
-        <v>2123</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="1294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1294" t="s">
-        <v>2144</v>
+        <v>1055</v>
       </c>
       <c r="B1294" t="s">
-        <v>2145</v>
+        <v>1056</v>
       </c>
       <c r="C1294" t="s">
-        <v>1573</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="1295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1295" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B1295" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C1295" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1296" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B1296" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C1296" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1297" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B1297" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C1297" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1298" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B1298" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C1298" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1299" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B1299" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C1299" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1300" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B1300" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C1300" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1301" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B1301" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C1301" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1302" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B1302" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C1302" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1303" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B1303" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C1303" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1304" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B1304" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C1304" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1305" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B1305" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C1305" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1306" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B1306" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C1306" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1307" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B1307" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C1307" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1308" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B1308" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C1308" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1309" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B1309" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C1309" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1310" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B1310" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C1310" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1311" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B1311" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C1311" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1312" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B1312" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C1312" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1313" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B1313" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C1313" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1314" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B1314" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C1314" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1315" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B1315" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C1315" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1316" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B1316" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C1316" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1317" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B1317" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C1317" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1318" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B1318" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C1318" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1319" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B1319" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C1319" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1320" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B1320" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C1320" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1321" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B1321" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C1321" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1322" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B1322" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C1322" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1323" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B1323" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C1323" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1324" t="s">
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1325" s="4" t="s">
+        <v>2116</v>
+      </c>
+      <c r="B1325" s="4" t="s">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1326" s="4" t="s">
+        <v>2117</v>
+      </c>
+      <c r="B1326" s="4" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1327" s="4" t="s">
+        <v>2118</v>
+      </c>
+      <c r="B1327" s="4" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1328" s="4" t="s">
+        <v>2119</v>
+      </c>
+      <c r="B1328" s="4" t="s">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1329" s="5" t="s">
+        <v>2120</v>
+      </c>
+      <c r="B1329" s="5" t="s">
+        <v>2129</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1330" t="s">
+        <v>2130</v>
+      </c>
+      <c r="B1330" t="s">
+        <v>2131</v>
+      </c>
+      <c r="C1330" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1331" t="s">
+        <v>2132</v>
+      </c>
+      <c r="B1331" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1331" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1332" t="s">
+        <v>2134</v>
+      </c>
+      <c r="B1332" t="s">
+        <v>2135</v>
+      </c>
+      <c r="C1332" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1333" t="s">
+        <v>2136</v>
+      </c>
+      <c r="B1333" t="s">
+        <v>2137</v>
+      </c>
+      <c r="C1333" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1334" t="s">
+        <v>2138</v>
+      </c>
+      <c r="B1334" t="s">
+        <v>2139</v>
+      </c>
+      <c r="C1334" t="s">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1335" t="s">
+        <v>2140</v>
+      </c>
+      <c r="B1335" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1335" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1336" t="s">
+        <v>2142</v>
+      </c>
+      <c r="B1336" t="s">
+        <v>2143</v>
+      </c>
+      <c r="C1336" t="s">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1337" t="s">
+        <v>2144</v>
+      </c>
+      <c r="B1337" t="s">
+        <v>2145</v>
+      </c>
+      <c r="C1337" t="s">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1338" t="s">
         <v>2146</v>
       </c>
-      <c r="B1295" t="s">
+      <c r="B1338" t="s">
         <v>2147</v>
       </c>
-      <c r="C1295" t="s">
+      <c r="C1338" t="s">
         <v>742</v>
       </c>
     </row>

--- a/00-日文單字.xlsx
+++ b/00-日文單字.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://guandamachine-my.sharepoint.com/personal/ec03_gd_guandamachine_com_tw/Documents/Fly/日語/日語練習網站/database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="220" documentId="11_AD4DBB64A54DDB1B405E38AFBD9A2E1F4F90DF1A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F378DC1-25AF-4D3F-9D86-E2CA63939C41}"/>
+  <xr:revisionPtr revIDLastSave="226" documentId="11_AD4DBB64A54DDB1B405E38AFBD9A2E1F4F90DF1A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DF05A15-5B80-4E88-863B-140CDCB716AC}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3546" uniqueCount="3080">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3611" uniqueCount="3138">
   <si>
     <t>わたし</t>
   </si>
@@ -9469,6 +9469,181 @@
   </si>
   <si>
     <t>圖書館前(虛構的車站名)</t>
+  </si>
+  <si>
+    <t>*第24課</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>くれます</t>
+  </si>
+  <si>
+    <t>給(我)</t>
+  </si>
+  <si>
+    <t>つれて いきます</t>
+  </si>
+  <si>
+    <t>連れて 行きます</t>
+  </si>
+  <si>
+    <t>帶(某人)去</t>
+  </si>
+  <si>
+    <t>つれて きます</t>
+  </si>
+  <si>
+    <t>連れて 来ます</t>
+  </si>
+  <si>
+    <t>帶(某人)來</t>
+  </si>
+  <si>
+    <t>送[人](去某處)</t>
+  </si>
+  <si>
+    <t>おくります ひとを～</t>
+  </si>
+  <si>
+    <t>送ります 人を～</t>
+  </si>
+  <si>
+    <t xml:space="preserve">送[人](去某處) </t>
+  </si>
+  <si>
+    <t>しょうかいします</t>
+  </si>
+  <si>
+    <t>紹介します</t>
+  </si>
+  <si>
+    <t>介紹</t>
+  </si>
+  <si>
+    <t>あんないします</t>
+  </si>
+  <si>
+    <t>案内します</t>
+  </si>
+  <si>
+    <t>帶路,引路</t>
+  </si>
+  <si>
+    <t>せつめいします</t>
+  </si>
+  <si>
+    <t>説明します</t>
+  </si>
+  <si>
+    <t>說明</t>
+  </si>
+  <si>
+    <t>いれます</t>
+  </si>
+  <si>
+    <t>沖,泡[咖啡]</t>
+  </si>
+  <si>
+    <t>コーヒーを いれます</t>
+  </si>
+  <si>
+    <t>おじいさん</t>
+  </si>
+  <si>
+    <t>祖父,老爺爺</t>
+  </si>
+  <si>
+    <t>おじいちゃん</t>
+  </si>
+  <si>
+    <t>おばあさん</t>
+  </si>
+  <si>
+    <t>祖母,老奶奶</t>
+  </si>
+  <si>
+    <t>おばあちゃん</t>
+  </si>
+  <si>
+    <t>じゅんび</t>
+  </si>
+  <si>
+    <t>準備</t>
+  </si>
+  <si>
+    <t>じゅんびします</t>
+  </si>
+  <si>
+    <t>準備します</t>
+  </si>
+  <si>
+    <t>做準備</t>
+  </si>
+  <si>
+    <t>いみ</t>
+  </si>
+  <si>
+    <t>意味</t>
+  </si>
+  <si>
+    <t>意思</t>
+  </si>
+  <si>
+    <t>[お]かし</t>
+  </si>
+  <si>
+    <t>[お]菓子</t>
+  </si>
+  <si>
+    <t>糕點,點心</t>
+  </si>
+  <si>
+    <t>ぜんぶ</t>
+  </si>
+  <si>
+    <t>全部</t>
+  </si>
+  <si>
+    <t>じぶんで</t>
+  </si>
+  <si>
+    <t>自分で</t>
+  </si>
+  <si>
+    <t>自己～</t>
+  </si>
+  <si>
+    <t>ほかに</t>
+  </si>
+  <si>
+    <t>另外</t>
+  </si>
+  <si>
+    <t>ワゴンしゃ</t>
+  </si>
+  <si>
+    <t>ワゴン車</t>
+  </si>
+  <si>
+    <t>旅行車</t>
+  </si>
+  <si>
+    <t>おべん とう</t>
+  </si>
+  <si>
+    <t>お弁当</t>
+  </si>
+  <si>
+    <t>餐盒,便當</t>
+  </si>
+  <si>
+    <t>ははのひ</t>
+  </si>
+  <si>
+    <t>母の日</t>
+  </si>
+  <si>
+    <t>母親節</t>
   </si>
 </sst>
 </file>
@@ -9837,7 +10012,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1338"/>
+  <dimension ref="A1:C1363"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="55.625" customWidth="1"/>
@@ -20023,3281 +20198,3526 @@
     </row>
     <row r="1034" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1034" t="s">
-        <v>455</v>
+        <v>3080</v>
       </c>
     </row>
     <row r="1035" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1035" t="s">
-        <v>457</v>
-      </c>
-      <c r="B1035" t="s">
-        <v>456</v>
+        <v>3081</v>
       </c>
       <c r="C1035" t="s">
-        <v>456</v>
+        <v>3082</v>
       </c>
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1036" t="s">
-        <v>460</v>
+        <v>3083</v>
       </c>
       <c r="B1036" t="s">
-        <v>459</v>
+        <v>3084</v>
       </c>
       <c r="C1036" t="s">
-        <v>458</v>
+        <v>3085</v>
       </c>
     </row>
     <row r="1037" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1037" t="s">
-        <v>463</v>
+        <v>3086</v>
       </c>
       <c r="B1037" t="s">
-        <v>462</v>
+        <v>3087</v>
       </c>
       <c r="C1037" t="s">
-        <v>461</v>
+        <v>3088</v>
       </c>
     </row>
     <row r="1038" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1038" t="s">
-        <v>465</v>
+        <v>1564</v>
       </c>
       <c r="B1038" t="s">
-        <v>464</v>
+        <v>1565</v>
       </c>
       <c r="C1038" t="s">
-        <v>464</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="1039" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1039" t="s">
-        <v>380</v>
+        <v>3090</v>
       </c>
       <c r="B1039" t="s">
-        <v>381</v>
+        <v>3091</v>
       </c>
       <c r="C1039" t="s">
-        <v>382</v>
+        <v>3092</v>
       </c>
     </row>
     <row r="1040" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1040" t="s">
-        <v>468</v>
+        <v>3093</v>
       </c>
       <c r="B1040" t="s">
-        <v>467</v>
+        <v>3094</v>
       </c>
       <c r="C1040" t="s">
-        <v>466</v>
+        <v>3095</v>
       </c>
     </row>
     <row r="1041" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1041" t="s">
-        <v>471</v>
+        <v>3096</v>
       </c>
       <c r="B1041" t="s">
-        <v>470</v>
+        <v>3097</v>
       </c>
       <c r="C1041" t="s">
-        <v>469</v>
+        <v>3098</v>
       </c>
     </row>
     <row r="1042" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1042" t="s">
-        <v>397</v>
+        <v>3099</v>
       </c>
       <c r="B1042" t="s">
-        <v>398</v>
+        <v>3100</v>
       </c>
       <c r="C1042" t="s">
-        <v>399</v>
+        <v>3101</v>
       </c>
     </row>
     <row r="1043" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1043" t="s">
-        <v>473</v>
-      </c>
-      <c r="B1043" t="s">
-        <v>472</v>
+        <v>3102</v>
       </c>
       <c r="C1043" t="s">
-        <v>472</v>
+        <v>3103</v>
       </c>
     </row>
     <row r="1044" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1044" t="s">
-        <v>475</v>
-      </c>
-      <c r="B1044" t="s">
-        <v>474</v>
+        <v>3104</v>
       </c>
       <c r="C1044" t="s">
-        <v>474</v>
+        <v>3103</v>
       </c>
     </row>
     <row r="1045" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1045" t="s">
-        <v>161</v>
-      </c>
-      <c r="B1045" t="s">
-        <v>162</v>
+        <v>3105</v>
       </c>
       <c r="C1045" t="s">
-        <v>163</v>
+        <v>3106</v>
       </c>
     </row>
     <row r="1046" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1046" t="s">
-        <v>478</v>
-      </c>
-      <c r="B1046" t="s">
-        <v>477</v>
+        <v>3107</v>
       </c>
       <c r="C1046" t="s">
-        <v>476</v>
+        <v>3106</v>
       </c>
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1047" t="s">
-        <v>364</v>
-      </c>
-      <c r="B1047" t="s">
-        <v>365</v>
+        <v>3108</v>
       </c>
       <c r="C1047" t="s">
-        <v>365</v>
+        <v>3109</v>
       </c>
     </row>
     <row r="1048" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1048" t="s">
-        <v>481</v>
-      </c>
-      <c r="B1048" t="s">
-        <v>480</v>
+        <v>3110</v>
       </c>
       <c r="C1048" t="s">
-        <v>479</v>
+        <v>3109</v>
       </c>
     </row>
     <row r="1049" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1049" t="s">
-        <v>484</v>
+        <v>3111</v>
       </c>
       <c r="B1049" t="s">
-        <v>483</v>
+        <v>3112</v>
       </c>
       <c r="C1049" t="s">
-        <v>482</v>
+        <v>3112</v>
       </c>
     </row>
     <row r="1050" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1050" t="s">
-        <v>487</v>
+        <v>3113</v>
       </c>
       <c r="B1050" t="s">
-        <v>486</v>
+        <v>3114</v>
       </c>
       <c r="C1050" t="s">
-        <v>485</v>
+        <v>3115</v>
       </c>
     </row>
     <row r="1051" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1051" t="s">
-        <v>490</v>
+        <v>3116</v>
       </c>
       <c r="B1051" t="s">
-        <v>489</v>
+        <v>3117</v>
       </c>
       <c r="C1051" t="s">
-        <v>488</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="1052" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1052" t="s">
-        <v>493</v>
+        <v>3119</v>
       </c>
       <c r="B1052" t="s">
-        <v>492</v>
+        <v>3120</v>
       </c>
       <c r="C1052" t="s">
-        <v>491</v>
+        <v>3121</v>
       </c>
     </row>
     <row r="1053" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1053" t="s">
-        <v>496</v>
+        <v>3122</v>
       </c>
       <c r="B1053" t="s">
-        <v>495</v>
+        <v>3123</v>
       </c>
       <c r="C1053" t="s">
-        <v>494</v>
+        <v>3123</v>
       </c>
     </row>
     <row r="1054" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1054" t="s">
-        <v>499</v>
+        <v>3124</v>
       </c>
       <c r="B1054" t="s">
-        <v>498</v>
+        <v>3125</v>
       </c>
       <c r="C1054" t="s">
-        <v>497</v>
+        <v>3126</v>
       </c>
     </row>
     <row r="1055" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1055" t="s">
-        <v>502</v>
-      </c>
-      <c r="B1055" t="s">
-        <v>501</v>
+        <v>3127</v>
       </c>
       <c r="C1055" t="s">
-        <v>500</v>
+        <v>3128</v>
       </c>
     </row>
     <row r="1056" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1056" t="s">
-        <v>504</v>
+        <v>3129</v>
       </c>
       <c r="B1056" t="s">
-        <v>503</v>
+        <v>3130</v>
       </c>
       <c r="C1056" t="s">
-        <v>503</v>
+        <v>3131</v>
       </c>
     </row>
     <row r="1057" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1057" t="s">
-        <v>507</v>
+        <v>3132</v>
       </c>
       <c r="B1057" t="s">
-        <v>506</v>
+        <v>3133</v>
       </c>
       <c r="C1057" t="s">
-        <v>505</v>
+        <v>3134</v>
       </c>
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1058" t="s">
-        <v>510</v>
+        <v>3135</v>
       </c>
       <c r="B1058" t="s">
-        <v>509</v>
+        <v>3136</v>
       </c>
       <c r="C1058" t="s">
-        <v>508</v>
+        <v>3137</v>
       </c>
     </row>
     <row r="1059" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1059" t="s">
-        <v>512</v>
-      </c>
-      <c r="B1059" t="s">
-        <v>390</v>
-      </c>
-      <c r="C1059" t="s">
-        <v>511</v>
+        <v>455</v>
       </c>
     </row>
     <row r="1060" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1060" t="s">
-        <v>515</v>
+        <v>457</v>
       </c>
       <c r="B1060" t="s">
-        <v>514</v>
+        <v>456</v>
       </c>
       <c r="C1060" t="s">
-        <v>513</v>
+        <v>456</v>
       </c>
     </row>
     <row r="1061" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1061" t="s">
-        <v>517</v>
+        <v>460</v>
       </c>
       <c r="B1061" t="s">
-        <v>383</v>
+        <v>459</v>
       </c>
       <c r="C1061" t="s">
-        <v>516</v>
+        <v>458</v>
       </c>
     </row>
     <row r="1062" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1062" t="s">
-        <v>519</v>
+        <v>463</v>
       </c>
       <c r="B1062" t="s">
-        <v>518</v>
+        <v>462</v>
       </c>
       <c r="C1062" t="s">
-        <v>518</v>
+        <v>461</v>
       </c>
     </row>
     <row r="1063" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1063" t="s">
-        <v>522</v>
+        <v>465</v>
       </c>
       <c r="B1063" t="s">
-        <v>521</v>
+        <v>464</v>
       </c>
       <c r="C1063" t="s">
-        <v>520</v>
+        <v>464</v>
       </c>
     </row>
     <row r="1064" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1064" t="s">
-        <v>523</v>
+        <v>380</v>
+      </c>
+      <c r="B1064" t="s">
+        <v>381</v>
+      </c>
+      <c r="C1064" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="1065" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1065" t="s">
-        <v>526</v>
+        <v>468</v>
       </c>
       <c r="B1065" t="s">
-        <v>525</v>
+        <v>467</v>
       </c>
       <c r="C1065" t="s">
-        <v>524</v>
+        <v>466</v>
       </c>
     </row>
     <row r="1066" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1066" t="s">
-        <v>529</v>
+        <v>471</v>
       </c>
       <c r="B1066" t="s">
-        <v>528</v>
+        <v>470</v>
       </c>
       <c r="C1066" t="s">
-        <v>527</v>
+        <v>469</v>
       </c>
     </row>
     <row r="1067" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1067" t="s">
-        <v>532</v>
+        <v>397</v>
       </c>
       <c r="B1067" t="s">
-        <v>531</v>
+        <v>398</v>
       </c>
       <c r="C1067" t="s">
-        <v>530</v>
+        <v>399</v>
       </c>
     </row>
     <row r="1068" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1068" t="s">
-        <v>535</v>
+        <v>473</v>
       </c>
       <c r="B1068" t="s">
-        <v>534</v>
+        <v>472</v>
       </c>
       <c r="C1068" t="s">
-        <v>533</v>
+        <v>472</v>
       </c>
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1069" t="s">
-        <v>538</v>
+        <v>475</v>
       </c>
       <c r="B1069" t="s">
-        <v>537</v>
+        <v>474</v>
       </c>
       <c r="C1069" t="s">
-        <v>536</v>
+        <v>474</v>
       </c>
     </row>
     <row r="1070" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1070" t="s">
-        <v>541</v>
+        <v>161</v>
       </c>
       <c r="B1070" t="s">
-        <v>540</v>
+        <v>162</v>
       </c>
       <c r="C1070" t="s">
-        <v>539</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1071" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1071" t="s">
-        <v>543</v>
+        <v>478</v>
       </c>
       <c r="B1071" t="s">
-        <v>542</v>
+        <v>477</v>
       </c>
       <c r="C1071" t="s">
-        <v>542</v>
+        <v>476</v>
       </c>
     </row>
     <row r="1072" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1072" t="s">
-        <v>545</v>
+        <v>364</v>
       </c>
       <c r="B1072" t="s">
-        <v>544</v>
+        <v>365</v>
       </c>
       <c r="C1072" t="s">
-        <v>544</v>
+        <v>365</v>
       </c>
     </row>
     <row r="1073" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1073" t="s">
-        <v>547</v>
+        <v>481</v>
       </c>
       <c r="B1073" t="s">
-        <v>546</v>
+        <v>480</v>
       </c>
       <c r="C1073" t="s">
-        <v>546</v>
+        <v>479</v>
       </c>
     </row>
     <row r="1074" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1074" t="s">
-        <v>549</v>
+        <v>484</v>
       </c>
       <c r="B1074" t="s">
-        <v>548</v>
+        <v>483</v>
       </c>
       <c r="C1074" t="s">
-        <v>548</v>
+        <v>482</v>
       </c>
     </row>
     <row r="1075" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1075" t="s">
-        <v>552</v>
+        <v>487</v>
       </c>
       <c r="B1075" t="s">
-        <v>551</v>
+        <v>486</v>
       </c>
       <c r="C1075" t="s">
-        <v>550</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1076" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1076" t="s">
-        <v>554</v>
+        <v>490</v>
       </c>
       <c r="B1076" t="s">
-        <v>553</v>
+        <v>489</v>
       </c>
       <c r="C1076" t="s">
-        <v>553</v>
+        <v>488</v>
       </c>
     </row>
     <row r="1077" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1077" t="s">
-        <v>557</v>
+        <v>493</v>
       </c>
       <c r="B1077" t="s">
-        <v>556</v>
+        <v>492</v>
       </c>
       <c r="C1077" t="s">
-        <v>555</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1078" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1078" t="s">
-        <v>559</v>
+        <v>496</v>
       </c>
       <c r="B1078" t="s">
-        <v>1126</v>
+        <v>495</v>
       </c>
       <c r="C1078" t="s">
-        <v>558</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1079" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1079" t="s">
-        <v>562</v>
+        <v>499</v>
       </c>
       <c r="B1079" t="s">
-        <v>561</v>
+        <v>498</v>
       </c>
       <c r="C1079" t="s">
-        <v>560</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1080" t="s">
-        <v>565</v>
+        <v>502</v>
       </c>
       <c r="B1080" t="s">
-        <v>564</v>
+        <v>501</v>
       </c>
       <c r="C1080" t="s">
-        <v>563</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1081" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1081" t="s">
-        <v>567</v>
+        <v>504</v>
       </c>
       <c r="B1081" t="s">
-        <v>566</v>
+        <v>503</v>
       </c>
       <c r="C1081" t="s">
-        <v>566</v>
+        <v>503</v>
       </c>
     </row>
     <row r="1082" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1082" t="s">
-        <v>570</v>
+        <v>507</v>
       </c>
       <c r="B1082" t="s">
-        <v>569</v>
+        <v>506</v>
       </c>
       <c r="C1082" t="s">
-        <v>568</v>
+        <v>505</v>
       </c>
     </row>
     <row r="1083" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1083" t="s">
-        <v>572</v>
+        <v>510</v>
       </c>
       <c r="B1083" t="s">
-        <v>571</v>
+        <v>509</v>
       </c>
       <c r="C1083" t="s">
-        <v>571</v>
+        <v>508</v>
       </c>
     </row>
     <row r="1084" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1084" t="s">
-        <v>575</v>
+        <v>512</v>
       </c>
       <c r="B1084" t="s">
-        <v>574</v>
+        <v>390</v>
       </c>
       <c r="C1084" t="s">
-        <v>573</v>
+        <v>511</v>
       </c>
     </row>
     <row r="1085" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1085" t="s">
-        <v>578</v>
+        <v>515</v>
       </c>
       <c r="B1085" t="s">
-        <v>577</v>
+        <v>514</v>
       </c>
       <c r="C1085" t="s">
-        <v>576</v>
+        <v>513</v>
       </c>
     </row>
     <row r="1086" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1086" t="s">
-        <v>581</v>
+        <v>517</v>
       </c>
       <c r="B1086" t="s">
-        <v>580</v>
+        <v>383</v>
       </c>
       <c r="C1086" t="s">
-        <v>579</v>
+        <v>516</v>
       </c>
     </row>
     <row r="1087" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1087" t="s">
-        <v>582</v>
+        <v>519</v>
       </c>
       <c r="B1087" t="s">
-        <v>120</v>
+        <v>518</v>
       </c>
       <c r="C1087" t="s">
-        <v>121</v>
+        <v>518</v>
       </c>
     </row>
     <row r="1088" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1088" t="s">
-        <v>585</v>
+        <v>522</v>
       </c>
       <c r="B1088" t="s">
-        <v>584</v>
+        <v>521</v>
       </c>
       <c r="C1088" t="s">
-        <v>583</v>
+        <v>520</v>
       </c>
     </row>
     <row r="1089" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1089" t="s">
-        <v>586</v>
+        <v>523</v>
       </c>
     </row>
     <row r="1090" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1090" t="s">
-        <v>589</v>
+        <v>526</v>
       </c>
       <c r="B1090" t="s">
-        <v>588</v>
+        <v>525</v>
       </c>
       <c r="C1090" t="s">
-        <v>587</v>
+        <v>524</v>
       </c>
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1091" t="s">
-        <v>592</v>
+        <v>529</v>
       </c>
       <c r="B1091" t="s">
-        <v>591</v>
+        <v>528</v>
       </c>
       <c r="C1091" t="s">
-        <v>590</v>
+        <v>527</v>
       </c>
     </row>
     <row r="1092" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1092" t="s">
-        <v>595</v>
+        <v>532</v>
       </c>
       <c r="B1092" t="s">
-        <v>594</v>
+        <v>531</v>
       </c>
       <c r="C1092" t="s">
-        <v>593</v>
+        <v>530</v>
       </c>
     </row>
     <row r="1093" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1093" t="s">
-        <v>598</v>
+        <v>535</v>
       </c>
       <c r="B1093" t="s">
-        <v>597</v>
+        <v>534</v>
       </c>
       <c r="C1093" t="s">
-        <v>596</v>
+        <v>533</v>
       </c>
     </row>
     <row r="1094" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1094" t="s">
-        <v>601</v>
+        <v>538</v>
       </c>
       <c r="B1094" t="s">
-        <v>600</v>
+        <v>537</v>
       </c>
       <c r="C1094" t="s">
-        <v>599</v>
+        <v>536</v>
       </c>
     </row>
     <row r="1095" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1095" t="s">
-        <v>604</v>
+        <v>541</v>
       </c>
       <c r="B1095" t="s">
-        <v>603</v>
+        <v>540</v>
       </c>
       <c r="C1095" t="s">
-        <v>602</v>
+        <v>539</v>
       </c>
     </row>
     <row r="1096" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1096" t="s">
-        <v>607</v>
+        <v>543</v>
       </c>
       <c r="B1096" t="s">
-        <v>606</v>
+        <v>542</v>
       </c>
       <c r="C1096" t="s">
-        <v>605</v>
+        <v>542</v>
       </c>
     </row>
     <row r="1097" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1097" t="s">
-        <v>610</v>
+        <v>545</v>
       </c>
       <c r="B1097" t="s">
-        <v>609</v>
+        <v>544</v>
       </c>
       <c r="C1097" t="s">
-        <v>608</v>
+        <v>544</v>
       </c>
     </row>
     <row r="1098" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1098" t="s">
-        <v>613</v>
+        <v>547</v>
       </c>
       <c r="B1098" t="s">
-        <v>612</v>
+        <v>546</v>
       </c>
       <c r="C1098" t="s">
-        <v>611</v>
+        <v>546</v>
       </c>
     </row>
     <row r="1099" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1099" t="s">
-        <v>616</v>
+        <v>549</v>
       </c>
       <c r="B1099" t="s">
-        <v>615</v>
+        <v>548</v>
       </c>
       <c r="C1099" t="s">
-        <v>614</v>
+        <v>548</v>
       </c>
     </row>
     <row r="1100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1100" t="s">
-        <v>619</v>
+        <v>552</v>
       </c>
       <c r="B1100" t="s">
-        <v>618</v>
+        <v>551</v>
       </c>
       <c r="C1100" t="s">
-        <v>617</v>
+        <v>550</v>
       </c>
     </row>
     <row r="1101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1101" t="s">
-        <v>404</v>
+        <v>554</v>
       </c>
       <c r="B1101" t="s">
-        <v>405</v>
+        <v>553</v>
       </c>
       <c r="C1101" t="s">
-        <v>406</v>
+        <v>553</v>
       </c>
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1102" t="s">
-        <v>622</v>
+        <v>557</v>
       </c>
       <c r="B1102" t="s">
-        <v>621</v>
+        <v>556</v>
       </c>
       <c r="C1102" t="s">
-        <v>620</v>
+        <v>555</v>
       </c>
     </row>
     <row r="1103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1103" t="s">
-        <v>58</v>
+        <v>559</v>
       </c>
       <c r="B1103" t="s">
-        <v>59</v>
+        <v>1126</v>
       </c>
       <c r="C1103" t="s">
-        <v>623</v>
+        <v>558</v>
       </c>
     </row>
     <row r="1104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1104" t="s">
-        <v>625</v>
+        <v>562</v>
       </c>
       <c r="B1104" t="s">
-        <v>624</v>
+        <v>561</v>
       </c>
       <c r="C1104" t="s">
-        <v>624</v>
+        <v>560</v>
       </c>
     </row>
     <row r="1105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1105" t="s">
-        <v>628</v>
+        <v>565</v>
       </c>
       <c r="B1105" t="s">
-        <v>627</v>
+        <v>564</v>
       </c>
       <c r="C1105" t="s">
-        <v>626</v>
+        <v>563</v>
       </c>
     </row>
     <row r="1106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1106" t="s">
-        <v>61</v>
+        <v>567</v>
       </c>
       <c r="B1106" t="s">
-        <v>62</v>
+        <v>566</v>
       </c>
       <c r="C1106" t="s">
-        <v>629</v>
+        <v>566</v>
       </c>
     </row>
     <row r="1107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1107" t="s">
-        <v>632</v>
+        <v>570</v>
       </c>
       <c r="B1107" t="s">
-        <v>631</v>
+        <v>569</v>
       </c>
       <c r="C1107" t="s">
-        <v>630</v>
+        <v>568</v>
       </c>
     </row>
     <row r="1108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1108" t="s">
-        <v>635</v>
+        <v>572</v>
       </c>
       <c r="B1108" t="s">
-        <v>634</v>
+        <v>571</v>
       </c>
       <c r="C1108" t="s">
-        <v>633</v>
+        <v>571</v>
       </c>
     </row>
     <row r="1109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1109" t="s">
-        <v>638</v>
+        <v>575</v>
       </c>
       <c r="B1109" t="s">
-        <v>637</v>
+        <v>574</v>
       </c>
       <c r="C1109" t="s">
-        <v>636</v>
+        <v>573</v>
       </c>
     </row>
     <row r="1110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1110" t="s">
-        <v>82</v>
+        <v>578</v>
       </c>
       <c r="B1110" t="s">
-        <v>83</v>
+        <v>577</v>
       </c>
       <c r="C1110" t="s">
-        <v>83</v>
+        <v>576</v>
       </c>
     </row>
     <row r="1111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1111" t="s">
-        <v>641</v>
+        <v>581</v>
       </c>
       <c r="B1111" t="s">
-        <v>640</v>
+        <v>580</v>
       </c>
       <c r="C1111" t="s">
-        <v>639</v>
+        <v>579</v>
       </c>
     </row>
     <row r="1112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1112" t="s">
-        <v>644</v>
+        <v>582</v>
       </c>
       <c r="B1112" t="s">
-        <v>643</v>
+        <v>120</v>
       </c>
       <c r="C1112" t="s">
-        <v>642</v>
+        <v>121</v>
       </c>
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1113" t="s">
-        <v>647</v>
+        <v>585</v>
       </c>
       <c r="B1113" t="s">
-        <v>646</v>
+        <v>584</v>
       </c>
       <c r="C1113" t="s">
-        <v>645</v>
+        <v>583</v>
       </c>
     </row>
     <row r="1114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1114" t="s">
-        <v>650</v>
-      </c>
-      <c r="B1114" t="s">
-        <v>649</v>
-      </c>
-      <c r="C1114" t="s">
-        <v>648</v>
+        <v>586</v>
       </c>
     </row>
     <row r="1115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1115" t="s">
-        <v>651</v>
+        <v>589</v>
       </c>
       <c r="B1115" t="s">
-        <v>70</v>
+        <v>588</v>
       </c>
       <c r="C1115" t="s">
-        <v>71</v>
+        <v>587</v>
       </c>
     </row>
     <row r="1116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1116" t="s">
-        <v>652</v>
+        <v>592</v>
       </c>
       <c r="B1116" t="s">
-        <v>84</v>
+        <v>591</v>
       </c>
       <c r="C1116" t="s">
-        <v>85</v>
+        <v>590</v>
       </c>
     </row>
     <row r="1117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1117" t="s">
-        <v>653</v>
+        <v>595</v>
       </c>
       <c r="B1117" t="s">
-        <v>86</v>
+        <v>594</v>
       </c>
       <c r="C1117" t="s">
-        <v>87</v>
+        <v>593</v>
       </c>
     </row>
     <row r="1118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1118" t="s">
-        <v>402</v>
+        <v>598</v>
       </c>
       <c r="B1118" t="s">
-        <v>403</v>
+        <v>597</v>
       </c>
       <c r="C1118" t="s">
-        <v>403</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1119" t="s">
-        <v>656</v>
+        <v>601</v>
       </c>
       <c r="B1119" t="s">
-        <v>655</v>
+        <v>600</v>
       </c>
       <c r="C1119" t="s">
-        <v>654</v>
+        <v>599</v>
       </c>
     </row>
     <row r="1120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1120" t="s">
-        <v>659</v>
+        <v>604</v>
       </c>
       <c r="B1120" t="s">
-        <v>658</v>
+        <v>603</v>
       </c>
       <c r="C1120" t="s">
-        <v>657</v>
+        <v>602</v>
       </c>
     </row>
     <row r="1121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1121" t="s">
-        <v>660</v>
+        <v>607</v>
       </c>
       <c r="B1121" t="s">
-        <v>102</v>
+        <v>606</v>
       </c>
       <c r="C1121" t="s">
-        <v>103</v>
+        <v>605</v>
       </c>
     </row>
     <row r="1122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1122" t="s">
-        <v>663</v>
+        <v>610</v>
       </c>
       <c r="B1122" t="s">
-        <v>662</v>
+        <v>609</v>
       </c>
       <c r="C1122" t="s">
-        <v>661</v>
+        <v>608</v>
       </c>
     </row>
     <row r="1123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1123" t="s">
-        <v>665</v>
+        <v>613</v>
       </c>
       <c r="B1123" t="s">
-        <v>106</v>
+        <v>612</v>
       </c>
       <c r="C1123" t="s">
-        <v>664</v>
+        <v>611</v>
       </c>
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1124" t="s">
-        <v>667</v>
+        <v>616</v>
       </c>
       <c r="B1124" t="s">
-        <v>666</v>
+        <v>615</v>
       </c>
       <c r="C1124" t="s">
-        <v>109</v>
+        <v>614</v>
       </c>
     </row>
     <row r="1125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1125" t="s">
-        <v>670</v>
+        <v>619</v>
       </c>
       <c r="B1125" t="s">
-        <v>669</v>
+        <v>618</v>
       </c>
       <c r="C1125" t="s">
-        <v>668</v>
+        <v>617</v>
       </c>
     </row>
     <row r="1126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1126" t="s">
-        <v>671</v>
+        <v>404</v>
+      </c>
+      <c r="B1126" t="s">
+        <v>405</v>
+      </c>
+      <c r="C1126" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="1127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1127" t="s">
-        <v>674</v>
+        <v>622</v>
       </c>
       <c r="B1127" t="s">
-        <v>673</v>
+        <v>621</v>
       </c>
       <c r="C1127" t="s">
-        <v>672</v>
+        <v>620</v>
       </c>
     </row>
     <row r="1128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1128" t="s">
-        <v>677</v>
+        <v>58</v>
       </c>
       <c r="B1128" t="s">
-        <v>676</v>
+        <v>59</v>
       </c>
       <c r="C1128" t="s">
-        <v>675</v>
+        <v>623</v>
       </c>
     </row>
     <row r="1129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1129" t="s">
-        <v>680</v>
+        <v>625</v>
       </c>
       <c r="B1129" t="s">
-        <v>679</v>
+        <v>624</v>
       </c>
       <c r="C1129" t="s">
-        <v>678</v>
+        <v>624</v>
       </c>
     </row>
     <row r="1130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1130" t="s">
-        <v>683</v>
+        <v>628</v>
       </c>
       <c r="B1130" t="s">
-        <v>682</v>
+        <v>627</v>
       </c>
       <c r="C1130" t="s">
-        <v>681</v>
+        <v>626</v>
       </c>
     </row>
     <row r="1131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1131" t="s">
-        <v>686</v>
+        <v>61</v>
       </c>
       <c r="B1131" t="s">
-        <v>685</v>
+        <v>62</v>
       </c>
       <c r="C1131" t="s">
-        <v>684</v>
+        <v>629</v>
       </c>
     </row>
     <row r="1132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1132" t="s">
-        <v>689</v>
+        <v>632</v>
       </c>
       <c r="B1132" t="s">
-        <v>688</v>
+        <v>631</v>
       </c>
       <c r="C1132" t="s">
-        <v>687</v>
+        <v>630</v>
       </c>
     </row>
     <row r="1133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1133" t="s">
-        <v>692</v>
+        <v>635</v>
       </c>
       <c r="B1133" t="s">
-        <v>691</v>
+        <v>634</v>
       </c>
       <c r="C1133" t="s">
-        <v>690</v>
+        <v>633</v>
       </c>
     </row>
     <row r="1134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1134" t="s">
-        <v>695</v>
+        <v>638</v>
       </c>
       <c r="B1134" t="s">
-        <v>694</v>
+        <v>637</v>
       </c>
       <c r="C1134" t="s">
-        <v>693</v>
+        <v>636</v>
       </c>
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1135" t="s">
-        <v>698</v>
+        <v>82</v>
       </c>
       <c r="B1135" t="s">
-        <v>697</v>
+        <v>83</v>
       </c>
       <c r="C1135" t="s">
-        <v>696</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1136" t="s">
-        <v>701</v>
+        <v>641</v>
       </c>
       <c r="B1136" t="s">
-        <v>700</v>
+        <v>640</v>
       </c>
       <c r="C1136" t="s">
-        <v>699</v>
+        <v>639</v>
       </c>
     </row>
     <row r="1137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1137" t="s">
-        <v>704</v>
+        <v>644</v>
       </c>
       <c r="B1137" t="s">
-        <v>703</v>
+        <v>643</v>
       </c>
       <c r="C1137" t="s">
-        <v>702</v>
+        <v>642</v>
       </c>
     </row>
     <row r="1138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1138" t="s">
-        <v>400</v>
+        <v>647</v>
       </c>
       <c r="B1138" t="s">
-        <v>706</v>
+        <v>646</v>
       </c>
       <c r="C1138" t="s">
-        <v>705</v>
+        <v>645</v>
       </c>
     </row>
     <row r="1139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1139" t="s">
-        <v>709</v>
+        <v>650</v>
       </c>
       <c r="B1139" t="s">
-        <v>708</v>
+        <v>649</v>
       </c>
       <c r="C1139" t="s">
-        <v>707</v>
+        <v>648</v>
       </c>
     </row>
     <row r="1140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1140" t="s">
-        <v>712</v>
+        <v>651</v>
       </c>
       <c r="B1140" t="s">
-        <v>711</v>
+        <v>70</v>
       </c>
       <c r="C1140" t="s">
-        <v>710</v>
+        <v>71</v>
       </c>
     </row>
     <row r="1141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1141" t="s">
-        <v>715</v>
+        <v>652</v>
       </c>
       <c r="B1141" t="s">
-        <v>714</v>
+        <v>84</v>
       </c>
       <c r="C1141" t="s">
-        <v>713</v>
+        <v>85</v>
       </c>
     </row>
     <row r="1142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1142" t="s">
-        <v>718</v>
+        <v>653</v>
       </c>
       <c r="B1142" t="s">
-        <v>717</v>
+        <v>86</v>
       </c>
       <c r="C1142" t="s">
-        <v>716</v>
+        <v>87</v>
       </c>
     </row>
     <row r="1143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1143" t="s">
-        <v>719</v>
+        <v>402</v>
+      </c>
+      <c r="B1143" t="s">
+        <v>403</v>
+      </c>
+      <c r="C1143" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="1144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1144" t="s">
-        <v>720</v>
-      </c>
-      <c r="B1144">
-        <v>1</v>
+        <v>656</v>
+      </c>
+      <c r="B1144" t="s">
+        <v>655</v>
       </c>
       <c r="C1144" t="s">
-        <v>1127</v>
+        <v>654</v>
       </c>
     </row>
     <row r="1145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1145" t="s">
-        <v>721</v>
-      </c>
-      <c r="B1145">
-        <v>2</v>
+        <v>659</v>
+      </c>
+      <c r="B1145" t="s">
+        <v>658</v>
       </c>
       <c r="C1145" t="s">
-        <v>1128</v>
+        <v>657</v>
       </c>
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1146" t="s">
-        <v>722</v>
-      </c>
-      <c r="B1146">
-        <v>3</v>
+        <v>660</v>
+      </c>
+      <c r="B1146" t="s">
+        <v>102</v>
       </c>
       <c r="C1146" t="s">
-        <v>1129</v>
+        <v>103</v>
       </c>
     </row>
     <row r="1147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1147" t="s">
-        <v>723</v>
-      </c>
-      <c r="B1147">
-        <v>4</v>
+        <v>663</v>
+      </c>
+      <c r="B1147" t="s">
+        <v>662</v>
       </c>
       <c r="C1147" t="s">
-        <v>1130</v>
+        <v>661</v>
       </c>
     </row>
     <row r="1148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1148" t="s">
-        <v>724</v>
-      </c>
-      <c r="B1148">
-        <v>5</v>
+        <v>665</v>
+      </c>
+      <c r="B1148" t="s">
+        <v>106</v>
       </c>
       <c r="C1148" t="s">
-        <v>1131</v>
+        <v>664</v>
       </c>
     </row>
     <row r="1149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1149" t="s">
-        <v>725</v>
-      </c>
-      <c r="B1149">
-        <v>6</v>
+        <v>667</v>
+      </c>
+      <c r="B1149" t="s">
+        <v>666</v>
       </c>
       <c r="C1149" t="s">
-        <v>1132</v>
+        <v>109</v>
       </c>
     </row>
     <row r="1150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1150" t="s">
-        <v>726</v>
-      </c>
-      <c r="B1150">
-        <v>7</v>
+        <v>670</v>
+      </c>
+      <c r="B1150" t="s">
+        <v>669</v>
       </c>
       <c r="C1150" t="s">
-        <v>1133</v>
+        <v>668</v>
       </c>
     </row>
     <row r="1151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1151" t="s">
-        <v>727</v>
-      </c>
-      <c r="B1151">
-        <v>8</v>
-      </c>
-      <c r="C1151" t="s">
-        <v>1134</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1152" t="s">
-        <v>728</v>
-      </c>
-      <c r="B1152">
-        <v>9</v>
+        <v>674</v>
+      </c>
+      <c r="B1152" t="s">
+        <v>673</v>
       </c>
       <c r="C1152" t="s">
-        <v>1135</v>
+        <v>672</v>
       </c>
     </row>
     <row r="1153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1153" t="s">
-        <v>729</v>
-      </c>
-      <c r="B1153">
-        <v>10</v>
+        <v>677</v>
+      </c>
+      <c r="B1153" t="s">
+        <v>676</v>
       </c>
       <c r="C1153" t="s">
-        <v>1136</v>
+        <v>675</v>
       </c>
     </row>
     <row r="1154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1154" t="s">
-        <v>1006</v>
-      </c>
-      <c r="B1154">
-        <v>20</v>
+        <v>680</v>
+      </c>
+      <c r="B1154" t="s">
+        <v>679</v>
       </c>
       <c r="C1154" t="s">
-        <v>1137</v>
+        <v>678</v>
       </c>
     </row>
     <row r="1155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1155" t="s">
-        <v>1007</v>
-      </c>
-      <c r="B1155">
-        <v>30</v>
+        <v>683</v>
+      </c>
+      <c r="B1155" t="s">
+        <v>682</v>
       </c>
       <c r="C1155" t="s">
-        <v>1138</v>
+        <v>681</v>
       </c>
     </row>
     <row r="1156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1156" t="s">
-        <v>1008</v>
-      </c>
-      <c r="B1156">
-        <v>40</v>
+        <v>686</v>
+      </c>
+      <c r="B1156" t="s">
+        <v>685</v>
       </c>
       <c r="C1156" t="s">
-        <v>1139</v>
+        <v>684</v>
       </c>
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1157" t="s">
-        <v>1009</v>
-      </c>
-      <c r="B1157">
-        <v>50</v>
+        <v>689</v>
+      </c>
+      <c r="B1157" t="s">
+        <v>688</v>
       </c>
       <c r="C1157" t="s">
-        <v>1140</v>
+        <v>687</v>
       </c>
     </row>
     <row r="1158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1158" t="s">
-        <v>1010</v>
-      </c>
-      <c r="B1158">
-        <v>60</v>
+        <v>692</v>
+      </c>
+      <c r="B1158" t="s">
+        <v>691</v>
       </c>
       <c r="C1158" t="s">
-        <v>1141</v>
+        <v>690</v>
       </c>
     </row>
     <row r="1159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1159" t="s">
-        <v>1011</v>
-      </c>
-      <c r="B1159">
-        <v>70</v>
+        <v>695</v>
+      </c>
+      <c r="B1159" t="s">
+        <v>694</v>
       </c>
       <c r="C1159" t="s">
-        <v>1142</v>
+        <v>693</v>
       </c>
     </row>
     <row r="1160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1160" t="s">
-        <v>1012</v>
-      </c>
-      <c r="B1160">
-        <v>80</v>
+        <v>698</v>
+      </c>
+      <c r="B1160" t="s">
+        <v>697</v>
       </c>
       <c r="C1160" t="s">
-        <v>1143</v>
+        <v>696</v>
       </c>
     </row>
     <row r="1161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1161" t="s">
-        <v>1013</v>
-      </c>
-      <c r="B1161">
-        <v>90</v>
+        <v>701</v>
+      </c>
+      <c r="B1161" t="s">
+        <v>700</v>
       </c>
       <c r="C1161" t="s">
-        <v>1144</v>
+        <v>699</v>
       </c>
     </row>
     <row r="1162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1162" t="s">
-        <v>429</v>
-      </c>
-      <c r="B1162">
-        <v>100</v>
+        <v>704</v>
+      </c>
+      <c r="B1162" t="s">
+        <v>703</v>
       </c>
       <c r="C1162" t="s">
-        <v>430</v>
+        <v>702</v>
       </c>
     </row>
     <row r="1163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1163" t="s">
-        <v>1014</v>
-      </c>
-      <c r="B1163">
-        <v>200</v>
+        <v>400</v>
+      </c>
+      <c r="B1163" t="s">
+        <v>706</v>
       </c>
       <c r="C1163" t="s">
-        <v>1145</v>
+        <v>705</v>
       </c>
     </row>
     <row r="1164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1164" t="s">
-        <v>1015</v>
-      </c>
-      <c r="B1164">
-        <v>300</v>
+        <v>709</v>
+      </c>
+      <c r="B1164" t="s">
+        <v>708</v>
       </c>
       <c r="C1164" t="s">
-        <v>1146</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1165" t="s">
-        <v>1016</v>
-      </c>
-      <c r="B1165">
-        <v>400</v>
+        <v>712</v>
+      </c>
+      <c r="B1165" t="s">
+        <v>711</v>
       </c>
       <c r="C1165" t="s">
-        <v>1147</v>
+        <v>710</v>
       </c>
     </row>
     <row r="1166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1166" t="s">
-        <v>1017</v>
-      </c>
-      <c r="B1166">
-        <v>500</v>
+        <v>715</v>
+      </c>
+      <c r="B1166" t="s">
+        <v>714</v>
       </c>
       <c r="C1166" t="s">
-        <v>1148</v>
+        <v>713</v>
       </c>
     </row>
     <row r="1167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1167" t="s">
-        <v>1018</v>
-      </c>
-      <c r="B1167">
-        <v>600</v>
+        <v>718</v>
+      </c>
+      <c r="B1167" t="s">
+        <v>717</v>
       </c>
       <c r="C1167" t="s">
-        <v>1149</v>
+        <v>716</v>
       </c>
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1168" t="s">
-        <v>1019</v>
-      </c>
-      <c r="B1168">
-        <v>700</v>
-      </c>
-      <c r="C1168" t="s">
-        <v>1150</v>
+        <v>719</v>
       </c>
     </row>
     <row r="1169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1169" t="s">
-        <v>1020</v>
+        <v>720</v>
       </c>
       <c r="B1169">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="C1169" t="s">
-        <v>1151</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="1170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1170" t="s">
-        <v>1021</v>
+        <v>721</v>
       </c>
       <c r="B1170">
-        <v>900</v>
+        <v>2</v>
       </c>
       <c r="C1170" t="s">
-        <v>1152</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="1171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1171" t="s">
-        <v>431</v>
+        <v>722</v>
       </c>
       <c r="B1171">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="C1171" t="s">
-        <v>432</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="1172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1172" t="s">
-        <v>1022</v>
+        <v>723</v>
       </c>
       <c r="B1172">
-        <v>2000</v>
+        <v>4</v>
       </c>
       <c r="C1172" t="s">
-        <v>1153</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="1173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1173" t="s">
-        <v>1023</v>
+        <v>724</v>
       </c>
       <c r="B1173">
-        <v>3000</v>
+        <v>5</v>
       </c>
       <c r="C1173" t="s">
-        <v>1154</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="1174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1174" t="s">
-        <v>1024</v>
+        <v>725</v>
       </c>
       <c r="B1174">
-        <v>4000</v>
+        <v>6</v>
       </c>
       <c r="C1174" t="s">
-        <v>1155</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="1175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1175" t="s">
-        <v>1025</v>
+        <v>726</v>
       </c>
       <c r="B1175">
-        <v>5000</v>
+        <v>7</v>
       </c>
       <c r="C1175" t="s">
-        <v>1156</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="1176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1176" t="s">
-        <v>1026</v>
+        <v>727</v>
       </c>
       <c r="B1176">
-        <v>6000</v>
+        <v>8</v>
       </c>
       <c r="C1176" t="s">
-        <v>1157</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="1177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1177" t="s">
-        <v>1027</v>
+        <v>728</v>
       </c>
       <c r="B1177">
-        <v>7000</v>
+        <v>9</v>
       </c>
       <c r="C1177" t="s">
-        <v>1158</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="1178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1178" t="s">
-        <v>1028</v>
+        <v>729</v>
       </c>
       <c r="B1178">
-        <v>8000</v>
+        <v>10</v>
       </c>
       <c r="C1178" t="s">
-        <v>1159</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1179" t="s">
-        <v>1029</v>
+        <v>1006</v>
       </c>
       <c r="B1179">
-        <v>9000</v>
+        <v>20</v>
       </c>
       <c r="C1179" t="s">
-        <v>1160</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="1180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1180" t="s">
-        <v>1030</v>
-      </c>
-      <c r="B1180" t="s">
-        <v>1161</v>
+        <v>1007</v>
+      </c>
+      <c r="B1180">
+        <v>30</v>
       </c>
       <c r="C1180" t="s">
-        <v>435</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="1181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1181" t="s">
-        <v>1031</v>
+        <v>1008</v>
       </c>
       <c r="B1181">
-        <v>20000</v>
+        <v>40</v>
       </c>
       <c r="C1181" t="s">
-        <v>1162</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="1182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1182" t="s">
-        <v>1032</v>
+        <v>1009</v>
       </c>
       <c r="B1182">
-        <v>30000</v>
+        <v>50</v>
       </c>
       <c r="C1182" t="s">
-        <v>1163</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="1183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1183" t="s">
-        <v>1033</v>
+        <v>1010</v>
       </c>
       <c r="B1183">
-        <v>40000</v>
+        <v>60</v>
       </c>
       <c r="C1183" t="s">
-        <v>1164</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="1184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1184" t="s">
-        <v>1034</v>
+        <v>1011</v>
       </c>
       <c r="B1184">
-        <v>50000</v>
+        <v>70</v>
       </c>
       <c r="C1184" t="s">
-        <v>1165</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="1185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1185" t="s">
-        <v>1035</v>
+        <v>1012</v>
       </c>
       <c r="B1185">
-        <v>60000</v>
+        <v>80</v>
       </c>
       <c r="C1185" t="s">
-        <v>1166</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="1186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1186" t="s">
-        <v>1036</v>
+        <v>1013</v>
       </c>
       <c r="B1186">
-        <v>70000</v>
+        <v>90</v>
       </c>
       <c r="C1186" t="s">
-        <v>1167</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="1187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1187" t="s">
-        <v>1037</v>
+        <v>429</v>
       </c>
       <c r="B1187">
-        <v>80000</v>
+        <v>100</v>
       </c>
       <c r="C1187" t="s">
-        <v>1168</v>
+        <v>430</v>
       </c>
     </row>
     <row r="1188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1188" t="s">
-        <v>1038</v>
+        <v>1014</v>
       </c>
       <c r="B1188">
-        <v>90000</v>
+        <v>200</v>
       </c>
       <c r="C1188" t="s">
-        <v>1169</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="1189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1189" t="s">
-        <v>433</v>
-      </c>
-      <c r="B1189" t="s">
-        <v>434</v>
+        <v>1015</v>
+      </c>
+      <c r="B1189">
+        <v>300</v>
       </c>
       <c r="C1189" t="s">
-        <v>435</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1190" t="s">
-        <v>1039</v>
-      </c>
-      <c r="B1190" t="s">
-        <v>1170</v>
+        <v>1016</v>
+      </c>
+      <c r="B1190">
+        <v>400</v>
       </c>
       <c r="C1190" t="s">
-        <v>1170</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="1191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1191" t="s">
-        <v>1171</v>
-      </c>
-      <c r="B1191" t="s">
-        <v>1172</v>
+        <v>1017</v>
+      </c>
+      <c r="B1191">
+        <v>500</v>
       </c>
       <c r="C1191" t="s">
-        <v>1172</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="1192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1192" t="s">
-        <v>1005</v>
+        <v>1018</v>
+      </c>
+      <c r="B1192">
+        <v>600</v>
+      </c>
+      <c r="C1192" t="s">
+        <v>1149</v>
       </c>
     </row>
     <row r="1193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1193" t="s">
-        <v>732</v>
-      </c>
-      <c r="B1193" t="s">
-        <v>731</v>
+        <v>1019</v>
+      </c>
+      <c r="B1193">
+        <v>700</v>
       </c>
       <c r="C1193" t="s">
-        <v>730</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="1194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1194" t="s">
-        <v>735</v>
-      </c>
-      <c r="B1194" t="s">
-        <v>734</v>
+        <v>1020</v>
+      </c>
+      <c r="B1194">
+        <v>800</v>
       </c>
       <c r="C1194" t="s">
-        <v>733</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="1195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1195" t="s">
-        <v>738</v>
-      </c>
-      <c r="B1195" t="s">
-        <v>737</v>
+        <v>1021</v>
+      </c>
+      <c r="B1195">
+        <v>900</v>
       </c>
       <c r="C1195" t="s">
-        <v>736</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="1196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1196" t="s">
-        <v>741</v>
-      </c>
-      <c r="B1196" t="s">
-        <v>740</v>
+        <v>431</v>
+      </c>
+      <c r="B1196">
+        <v>1000</v>
       </c>
       <c r="C1196" t="s">
-        <v>739</v>
+        <v>432</v>
       </c>
     </row>
     <row r="1197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1197" t="s">
-        <v>744</v>
-      </c>
-      <c r="B1197" t="s">
-        <v>743</v>
+        <v>1022</v>
+      </c>
+      <c r="B1197">
+        <v>2000</v>
       </c>
       <c r="C1197" t="s">
-        <v>742</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="1198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1198" t="s">
-        <v>747</v>
-      </c>
-      <c r="B1198" t="s">
-        <v>746</v>
+        <v>1023</v>
+      </c>
+      <c r="B1198">
+        <v>3000</v>
       </c>
       <c r="C1198" t="s">
-        <v>745</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="1199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1199" t="s">
-        <v>750</v>
-      </c>
-      <c r="B1199" t="s">
-        <v>749</v>
+        <v>1024</v>
+      </c>
+      <c r="B1199">
+        <v>4000</v>
       </c>
       <c r="C1199" t="s">
-        <v>748</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="1200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1200" t="s">
-        <v>753</v>
-      </c>
-      <c r="B1200" t="s">
-        <v>752</v>
+        <v>1025</v>
+      </c>
+      <c r="B1200">
+        <v>5000</v>
       </c>
       <c r="C1200" t="s">
-        <v>751</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1201" t="s">
-        <v>756</v>
-      </c>
-      <c r="B1201" t="s">
-        <v>755</v>
+        <v>1026</v>
+      </c>
+      <c r="B1201">
+        <v>6000</v>
       </c>
       <c r="C1201" t="s">
-        <v>754</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="1202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1202" t="s">
-        <v>759</v>
-      </c>
-      <c r="B1202" t="s">
-        <v>758</v>
+        <v>1027</v>
+      </c>
+      <c r="B1202">
+        <v>7000</v>
       </c>
       <c r="C1202" t="s">
-        <v>757</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="1203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1203" t="s">
-        <v>762</v>
-      </c>
-      <c r="B1203" t="s">
-        <v>761</v>
+        <v>1028</v>
+      </c>
+      <c r="B1203">
+        <v>8000</v>
       </c>
       <c r="C1203" t="s">
-        <v>760</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="1204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1204" t="s">
-        <v>765</v>
-      </c>
-      <c r="B1204" t="s">
-        <v>764</v>
+        <v>1029</v>
+      </c>
+      <c r="B1204">
+        <v>9000</v>
       </c>
       <c r="C1204" t="s">
-        <v>763</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="1205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1205" t="s">
-        <v>768</v>
+        <v>1030</v>
       </c>
       <c r="B1205" t="s">
-        <v>767</v>
+        <v>1161</v>
       </c>
       <c r="C1205" t="s">
-        <v>766</v>
+        <v>435</v>
       </c>
     </row>
     <row r="1206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1206" t="s">
-        <v>771</v>
-      </c>
-      <c r="B1206" t="s">
-        <v>770</v>
+        <v>1031</v>
+      </c>
+      <c r="B1206">
+        <v>20000</v>
       </c>
       <c r="C1206" t="s">
-        <v>769</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="1207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1207" t="s">
-        <v>774</v>
-      </c>
-      <c r="B1207" t="s">
-        <v>773</v>
+        <v>1032</v>
+      </c>
+      <c r="B1207">
+        <v>30000</v>
       </c>
       <c r="C1207" t="s">
-        <v>772</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="1208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1208" t="s">
-        <v>776</v>
-      </c>
-      <c r="B1208" t="s">
-        <v>775</v>
+        <v>1033</v>
+      </c>
+      <c r="B1208">
+        <v>40000</v>
       </c>
       <c r="C1208" t="s">
-        <v>301</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="1209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1209" t="s">
-        <v>779</v>
-      </c>
-      <c r="B1209" t="s">
-        <v>778</v>
+        <v>1034</v>
+      </c>
+      <c r="B1209">
+        <v>50000</v>
       </c>
       <c r="C1209" t="s">
-        <v>777</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="1210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1210" t="s">
-        <v>782</v>
-      </c>
-      <c r="B1210" t="s">
-        <v>781</v>
+        <v>1035</v>
+      </c>
+      <c r="B1210">
+        <v>60000</v>
       </c>
       <c r="C1210" t="s">
-        <v>780</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="1211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1211" t="s">
-        <v>785</v>
-      </c>
-      <c r="B1211" t="s">
-        <v>784</v>
+        <v>1036</v>
+      </c>
+      <c r="B1211">
+        <v>70000</v>
       </c>
       <c r="C1211" t="s">
-        <v>783</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1212" t="s">
-        <v>788</v>
-      </c>
-      <c r="B1212" t="s">
-        <v>787</v>
+        <v>1037</v>
+      </c>
+      <c r="B1212">
+        <v>80000</v>
       </c>
       <c r="C1212" t="s">
-        <v>786</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="1213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1213" t="s">
-        <v>791</v>
-      </c>
-      <c r="B1213" t="s">
-        <v>790</v>
+        <v>1038</v>
+      </c>
+      <c r="B1213">
+        <v>90000</v>
       </c>
       <c r="C1213" t="s">
-        <v>789</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="1214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1214" t="s">
-        <v>794</v>
+        <v>433</v>
       </c>
       <c r="B1214" t="s">
-        <v>793</v>
+        <v>434</v>
       </c>
       <c r="C1214" t="s">
-        <v>792</v>
+        <v>435</v>
       </c>
     </row>
     <row r="1215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1215" t="s">
-        <v>797</v>
+        <v>1039</v>
       </c>
       <c r="B1215" t="s">
-        <v>796</v>
+        <v>1170</v>
       </c>
       <c r="C1215" t="s">
-        <v>795</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="1216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1216" t="s">
-        <v>800</v>
+        <v>1171</v>
       </c>
       <c r="B1216" t="s">
-        <v>799</v>
+        <v>1172</v>
       </c>
       <c r="C1216" t="s">
-        <v>798</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="1217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1217" t="s">
-        <v>803</v>
-      </c>
-      <c r="B1217" t="s">
-        <v>802</v>
-      </c>
-      <c r="C1217" t="s">
-        <v>801</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="1218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1218" t="s">
-        <v>806</v>
+        <v>732</v>
       </c>
       <c r="B1218" t="s">
-        <v>805</v>
+        <v>731</v>
       </c>
       <c r="C1218" t="s">
-        <v>804</v>
+        <v>730</v>
       </c>
     </row>
     <row r="1219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1219" t="s">
-        <v>809</v>
+        <v>735</v>
       </c>
       <c r="B1219" t="s">
-        <v>808</v>
+        <v>734</v>
       </c>
       <c r="C1219" t="s">
-        <v>807</v>
+        <v>733</v>
       </c>
     </row>
     <row r="1220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1220" t="s">
-        <v>812</v>
+        <v>738</v>
       </c>
       <c r="B1220" t="s">
-        <v>811</v>
+        <v>737</v>
       </c>
       <c r="C1220" t="s">
-        <v>810</v>
+        <v>736</v>
       </c>
     </row>
     <row r="1221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1221" t="s">
-        <v>815</v>
+        <v>741</v>
       </c>
       <c r="B1221" t="s">
-        <v>814</v>
+        <v>740</v>
       </c>
       <c r="C1221" t="s">
-        <v>813</v>
+        <v>739</v>
       </c>
     </row>
     <row r="1222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1222" t="s">
-        <v>818</v>
+        <v>744</v>
       </c>
       <c r="B1222" t="s">
-        <v>817</v>
+        <v>743</v>
       </c>
       <c r="C1222" t="s">
-        <v>816</v>
+        <v>742</v>
       </c>
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1223" t="s">
-        <v>821</v>
+        <v>747</v>
       </c>
       <c r="B1223" t="s">
-        <v>820</v>
+        <v>746</v>
       </c>
       <c r="C1223" t="s">
-        <v>819</v>
+        <v>745</v>
       </c>
     </row>
     <row r="1224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1224" t="s">
-        <v>824</v>
+        <v>750</v>
       </c>
       <c r="B1224" t="s">
-        <v>823</v>
+        <v>749</v>
       </c>
       <c r="C1224" t="s">
-        <v>822</v>
+        <v>748</v>
       </c>
     </row>
     <row r="1225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1225" t="s">
-        <v>827</v>
+        <v>753</v>
       </c>
       <c r="B1225" t="s">
-        <v>826</v>
+        <v>752</v>
       </c>
       <c r="C1225" t="s">
-        <v>825</v>
+        <v>751</v>
       </c>
     </row>
     <row r="1226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1226" t="s">
-        <v>830</v>
+        <v>756</v>
       </c>
       <c r="B1226" t="s">
-        <v>829</v>
+        <v>755</v>
       </c>
       <c r="C1226" t="s">
-        <v>828</v>
+        <v>754</v>
       </c>
     </row>
     <row r="1227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1227" t="s">
-        <v>833</v>
+        <v>759</v>
       </c>
       <c r="B1227" t="s">
-        <v>832</v>
+        <v>758</v>
       </c>
       <c r="C1227" t="s">
-        <v>831</v>
+        <v>757</v>
       </c>
     </row>
     <row r="1228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1228" t="s">
-        <v>836</v>
+        <v>762</v>
       </c>
       <c r="B1228" t="s">
-        <v>835</v>
+        <v>761</v>
       </c>
       <c r="C1228" t="s">
-        <v>834</v>
+        <v>760</v>
       </c>
     </row>
     <row r="1229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1229" t="s">
-        <v>839</v>
+        <v>765</v>
       </c>
       <c r="B1229" t="s">
-        <v>838</v>
+        <v>764</v>
       </c>
       <c r="C1229" t="s">
-        <v>837</v>
+        <v>763</v>
       </c>
     </row>
     <row r="1230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1230" t="s">
-        <v>842</v>
+        <v>768</v>
       </c>
       <c r="B1230" t="s">
-        <v>841</v>
+        <v>767</v>
       </c>
       <c r="C1230" t="s">
-        <v>840</v>
+        <v>766</v>
       </c>
     </row>
     <row r="1231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1231" t="s">
-        <v>845</v>
+        <v>771</v>
       </c>
       <c r="B1231" t="s">
-        <v>844</v>
+        <v>770</v>
       </c>
       <c r="C1231" t="s">
-        <v>843</v>
+        <v>769</v>
       </c>
     </row>
     <row r="1232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1232" t="s">
-        <v>848</v>
+        <v>774</v>
       </c>
       <c r="B1232" t="s">
-        <v>847</v>
+        <v>773</v>
       </c>
       <c r="C1232" t="s">
-        <v>846</v>
+        <v>772</v>
       </c>
     </row>
     <row r="1233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1233" t="s">
-        <v>851</v>
+        <v>776</v>
       </c>
       <c r="B1233" t="s">
-        <v>850</v>
+        <v>775</v>
       </c>
       <c r="C1233" t="s">
-        <v>849</v>
+        <v>301</v>
       </c>
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1234" t="s">
-        <v>854</v>
+        <v>779</v>
       </c>
       <c r="B1234" t="s">
-        <v>853</v>
+        <v>778</v>
       </c>
       <c r="C1234" t="s">
-        <v>852</v>
+        <v>777</v>
       </c>
     </row>
     <row r="1235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1235" t="s">
-        <v>855</v>
+        <v>782</v>
+      </c>
+      <c r="B1235" t="s">
+        <v>781</v>
+      </c>
+      <c r="C1235" t="s">
+        <v>780</v>
       </c>
     </row>
     <row r="1236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1236" t="s">
-        <v>858</v>
+        <v>785</v>
       </c>
       <c r="B1236" t="s">
-        <v>857</v>
+        <v>784</v>
       </c>
       <c r="C1236" t="s">
-        <v>856</v>
+        <v>783</v>
       </c>
     </row>
     <row r="1237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1237" t="s">
-        <v>861</v>
+        <v>788</v>
       </c>
       <c r="B1237" t="s">
-        <v>860</v>
+        <v>787</v>
       </c>
       <c r="C1237" t="s">
-        <v>859</v>
+        <v>786</v>
       </c>
     </row>
     <row r="1238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1238" t="s">
-        <v>864</v>
+        <v>791</v>
       </c>
       <c r="B1238" t="s">
-        <v>863</v>
+        <v>790</v>
       </c>
       <c r="C1238" t="s">
-        <v>862</v>
+        <v>789</v>
       </c>
     </row>
     <row r="1239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1239" t="s">
-        <v>867</v>
+        <v>794</v>
       </c>
       <c r="B1239" t="s">
-        <v>866</v>
+        <v>793</v>
       </c>
       <c r="C1239" t="s">
-        <v>865</v>
+        <v>792</v>
       </c>
     </row>
     <row r="1240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1240" t="s">
-        <v>870</v>
+        <v>797</v>
       </c>
       <c r="B1240" t="s">
-        <v>869</v>
+        <v>796</v>
       </c>
       <c r="C1240" t="s">
-        <v>868</v>
+        <v>795</v>
       </c>
     </row>
     <row r="1241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1241" t="s">
-        <v>858</v>
+        <v>800</v>
       </c>
       <c r="B1241" t="s">
-        <v>872</v>
+        <v>799</v>
       </c>
       <c r="C1241" t="s">
-        <v>871</v>
+        <v>798</v>
       </c>
     </row>
     <row r="1242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1242" t="s">
-        <v>875</v>
+        <v>803</v>
       </c>
       <c r="B1242" t="s">
-        <v>874</v>
+        <v>802</v>
       </c>
       <c r="C1242" t="s">
-        <v>873</v>
+        <v>801</v>
       </c>
     </row>
     <row r="1243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1243" t="s">
-        <v>878</v>
+        <v>806</v>
       </c>
       <c r="B1243" t="s">
-        <v>877</v>
+        <v>805</v>
       </c>
       <c r="C1243" t="s">
-        <v>876</v>
+        <v>804</v>
       </c>
     </row>
     <row r="1244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1244" t="s">
-        <v>881</v>
+        <v>809</v>
       </c>
       <c r="B1244" t="s">
-        <v>880</v>
+        <v>808</v>
       </c>
       <c r="C1244" t="s">
-        <v>879</v>
+        <v>807</v>
       </c>
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1245" t="s">
-        <v>884</v>
+        <v>812</v>
       </c>
       <c r="B1245" t="s">
-        <v>883</v>
+        <v>811</v>
       </c>
       <c r="C1245" t="s">
-        <v>882</v>
+        <v>810</v>
       </c>
     </row>
     <row r="1246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1246" t="s">
-        <v>887</v>
+        <v>815</v>
       </c>
       <c r="B1246" t="s">
-        <v>886</v>
+        <v>814</v>
       </c>
       <c r="C1246" t="s">
-        <v>885</v>
+        <v>813</v>
       </c>
     </row>
     <row r="1247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1247" t="s">
-        <v>890</v>
+        <v>818</v>
       </c>
       <c r="B1247" t="s">
-        <v>889</v>
+        <v>817</v>
       </c>
       <c r="C1247" t="s">
-        <v>888</v>
+        <v>816</v>
       </c>
     </row>
     <row r="1248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1248" t="s">
-        <v>893</v>
+        <v>821</v>
       </c>
       <c r="B1248" t="s">
-        <v>892</v>
+        <v>820</v>
       </c>
       <c r="C1248" t="s">
-        <v>891</v>
+        <v>819</v>
       </c>
     </row>
     <row r="1249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1249" t="s">
-        <v>896</v>
+        <v>824</v>
       </c>
       <c r="B1249" t="s">
-        <v>895</v>
+        <v>823</v>
       </c>
       <c r="C1249" t="s">
-        <v>894</v>
+        <v>822</v>
       </c>
     </row>
     <row r="1250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1250" t="s">
-        <v>899</v>
+        <v>827</v>
       </c>
       <c r="B1250" t="s">
-        <v>898</v>
+        <v>826</v>
       </c>
       <c r="C1250" t="s">
-        <v>897</v>
+        <v>825</v>
       </c>
     </row>
     <row r="1251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1251" t="s">
-        <v>902</v>
+        <v>830</v>
       </c>
       <c r="B1251" t="s">
-        <v>901</v>
+        <v>829</v>
       </c>
       <c r="C1251" t="s">
-        <v>900</v>
+        <v>828</v>
       </c>
     </row>
     <row r="1252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1252" t="s">
-        <v>902</v>
+        <v>833</v>
       </c>
       <c r="B1252" t="s">
-        <v>904</v>
+        <v>832</v>
       </c>
       <c r="C1252" t="s">
-        <v>903</v>
+        <v>831</v>
       </c>
     </row>
     <row r="1253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1253" t="s">
-        <v>907</v>
+        <v>836</v>
       </c>
       <c r="B1253" t="s">
-        <v>906</v>
+        <v>835</v>
       </c>
       <c r="C1253" t="s">
-        <v>905</v>
+        <v>834</v>
       </c>
     </row>
     <row r="1254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1254" t="s">
-        <v>910</v>
+        <v>839</v>
       </c>
       <c r="B1254" t="s">
-        <v>909</v>
+        <v>838</v>
       </c>
       <c r="C1254" t="s">
-        <v>908</v>
+        <v>837</v>
       </c>
     </row>
     <row r="1255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1255" t="s">
-        <v>913</v>
+        <v>842</v>
       </c>
       <c r="B1255" t="s">
-        <v>912</v>
+        <v>841</v>
       </c>
       <c r="C1255" t="s">
-        <v>911</v>
+        <v>840</v>
       </c>
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1256" t="s">
-        <v>916</v>
+        <v>845</v>
       </c>
       <c r="B1256" t="s">
-        <v>915</v>
+        <v>844</v>
       </c>
       <c r="C1256" t="s">
-        <v>914</v>
+        <v>843</v>
       </c>
     </row>
     <row r="1257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1257" t="s">
-        <v>919</v>
+        <v>848</v>
       </c>
       <c r="B1257" t="s">
-        <v>918</v>
+        <v>847</v>
       </c>
       <c r="C1257" t="s">
-        <v>917</v>
+        <v>846</v>
       </c>
     </row>
     <row r="1258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1258" t="s">
-        <v>922</v>
+        <v>851</v>
       </c>
       <c r="B1258" t="s">
-        <v>921</v>
+        <v>850</v>
       </c>
       <c r="C1258" t="s">
-        <v>920</v>
+        <v>849</v>
       </c>
     </row>
     <row r="1259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1259" t="s">
-        <v>925</v>
+        <v>854</v>
       </c>
       <c r="B1259" t="s">
-        <v>924</v>
+        <v>853</v>
       </c>
       <c r="C1259" t="s">
-        <v>923</v>
+        <v>852</v>
       </c>
     </row>
     <row r="1260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1260" t="s">
-        <v>928</v>
-      </c>
-      <c r="B1260" t="s">
-        <v>927</v>
-      </c>
-      <c r="C1260" t="s">
-        <v>926</v>
+        <v>855</v>
       </c>
     </row>
     <row r="1261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1261" t="s">
-        <v>931</v>
+        <v>858</v>
       </c>
       <c r="B1261" t="s">
-        <v>930</v>
+        <v>857</v>
       </c>
       <c r="C1261" t="s">
-        <v>929</v>
+        <v>856</v>
       </c>
     </row>
     <row r="1262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1262" t="s">
-        <v>934</v>
+        <v>861</v>
       </c>
       <c r="B1262" t="s">
-        <v>933</v>
+        <v>860</v>
       </c>
       <c r="C1262" t="s">
-        <v>932</v>
+        <v>859</v>
       </c>
     </row>
     <row r="1263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1263" t="s">
-        <v>937</v>
+        <v>864</v>
       </c>
       <c r="B1263" t="s">
-        <v>936</v>
+        <v>863</v>
       </c>
       <c r="C1263" t="s">
-        <v>935</v>
+        <v>862</v>
       </c>
     </row>
     <row r="1264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1264" t="s">
-        <v>940</v>
+        <v>867</v>
       </c>
       <c r="B1264" t="s">
-        <v>939</v>
+        <v>866</v>
       </c>
       <c r="C1264" t="s">
-        <v>938</v>
+        <v>865</v>
       </c>
     </row>
     <row r="1265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1265" t="s">
-        <v>943</v>
+        <v>870</v>
       </c>
       <c r="B1265" t="s">
-        <v>942</v>
+        <v>869</v>
       </c>
       <c r="C1265" t="s">
-        <v>941</v>
+        <v>868</v>
       </c>
     </row>
     <row r="1266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1266" t="s">
-        <v>946</v>
+        <v>858</v>
       </c>
       <c r="B1266" t="s">
-        <v>945</v>
+        <v>872</v>
       </c>
       <c r="C1266" t="s">
-        <v>944</v>
+        <v>871</v>
       </c>
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1267" t="s">
-        <v>948</v>
+        <v>875</v>
       </c>
       <c r="B1267" t="s">
-        <v>948</v>
+        <v>874</v>
       </c>
       <c r="C1267" t="s">
-        <v>947</v>
+        <v>873</v>
       </c>
     </row>
     <row r="1268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1268" t="s">
-        <v>951</v>
+        <v>878</v>
       </c>
       <c r="B1268" t="s">
-        <v>950</v>
+        <v>877</v>
       </c>
       <c r="C1268" t="s">
-        <v>949</v>
+        <v>876</v>
       </c>
     </row>
     <row r="1269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1269" t="s">
-        <v>954</v>
+        <v>881</v>
       </c>
       <c r="B1269" t="s">
-        <v>953</v>
+        <v>880</v>
       </c>
       <c r="C1269" t="s">
-        <v>952</v>
+        <v>879</v>
       </c>
     </row>
     <row r="1270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1270" t="s">
-        <v>957</v>
+        <v>884</v>
       </c>
       <c r="B1270" t="s">
-        <v>956</v>
+        <v>883</v>
       </c>
       <c r="C1270" t="s">
-        <v>955</v>
+        <v>882</v>
       </c>
     </row>
     <row r="1271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1271" t="s">
-        <v>960</v>
+        <v>887</v>
       </c>
       <c r="B1271" t="s">
-        <v>959</v>
+        <v>886</v>
       </c>
       <c r="C1271" t="s">
-        <v>958</v>
+        <v>885</v>
       </c>
     </row>
     <row r="1272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1272" t="s">
-        <v>962</v>
+        <v>890</v>
+      </c>
+      <c r="B1272" t="s">
+        <v>889</v>
       </c>
       <c r="C1272" t="s">
-        <v>961</v>
+        <v>888</v>
       </c>
     </row>
     <row r="1273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1273" t="s">
-        <v>965</v>
+        <v>893</v>
       </c>
       <c r="B1273" t="s">
-        <v>964</v>
+        <v>892</v>
       </c>
       <c r="C1273" t="s">
-        <v>963</v>
+        <v>891</v>
       </c>
     </row>
     <row r="1274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1274" t="s">
-        <v>968</v>
+        <v>896</v>
       </c>
       <c r="B1274" t="s">
-        <v>967</v>
+        <v>895</v>
       </c>
       <c r="C1274" t="s">
-        <v>966</v>
+        <v>894</v>
       </c>
     </row>
     <row r="1275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1275" t="s">
-        <v>965</v>
+        <v>899</v>
       </c>
       <c r="B1275" t="s">
-        <v>970</v>
+        <v>898</v>
       </c>
       <c r="C1275" t="s">
-        <v>969</v>
+        <v>897</v>
       </c>
     </row>
     <row r="1276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1276" t="s">
-        <v>973</v>
+        <v>902</v>
       </c>
       <c r="B1276" t="s">
-        <v>972</v>
+        <v>901</v>
       </c>
       <c r="C1276" t="s">
-        <v>971</v>
+        <v>900</v>
       </c>
     </row>
     <row r="1277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1277" t="s">
-        <v>976</v>
+        <v>902</v>
       </c>
       <c r="B1277" t="s">
-        <v>975</v>
+        <v>904</v>
       </c>
       <c r="C1277" t="s">
-        <v>974</v>
+        <v>903</v>
       </c>
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1278" t="s">
-        <v>979</v>
+        <v>907</v>
       </c>
       <c r="B1278" t="s">
-        <v>978</v>
+        <v>906</v>
       </c>
       <c r="C1278" t="s">
-        <v>977</v>
+        <v>905</v>
       </c>
     </row>
     <row r="1279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1279" t="s">
-        <v>982</v>
+        <v>910</v>
       </c>
       <c r="B1279" t="s">
-        <v>981</v>
+        <v>909</v>
       </c>
       <c r="C1279" t="s">
-        <v>980</v>
+        <v>908</v>
       </c>
     </row>
     <row r="1280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1280" t="s">
-        <v>985</v>
+        <v>913</v>
       </c>
       <c r="B1280" t="s">
-        <v>984</v>
+        <v>912</v>
       </c>
       <c r="C1280" t="s">
-        <v>983</v>
+        <v>911</v>
       </c>
     </row>
     <row r="1281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1281" t="s">
-        <v>988</v>
+        <v>916</v>
       </c>
       <c r="B1281" t="s">
-        <v>987</v>
+        <v>915</v>
       </c>
       <c r="C1281" t="s">
-        <v>986</v>
+        <v>914</v>
       </c>
     </row>
     <row r="1282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1282" t="s">
-        <v>990</v>
+        <v>919</v>
+      </c>
+      <c r="B1282" t="s">
+        <v>918</v>
       </c>
       <c r="C1282" t="s">
-        <v>989</v>
+        <v>917</v>
       </c>
     </row>
     <row r="1283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1283" t="s">
-        <v>993</v>
+        <v>922</v>
       </c>
       <c r="B1283" t="s">
-        <v>992</v>
+        <v>921</v>
       </c>
       <c r="C1283" t="s">
-        <v>991</v>
+        <v>920</v>
       </c>
     </row>
     <row r="1284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1284" t="s">
-        <v>996</v>
+        <v>925</v>
       </c>
       <c r="B1284" t="s">
-        <v>995</v>
+        <v>924</v>
       </c>
       <c r="C1284" t="s">
-        <v>994</v>
+        <v>923</v>
       </c>
     </row>
     <row r="1285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1285" t="s">
-        <v>998</v>
+        <v>928</v>
       </c>
       <c r="B1285" t="s">
-        <v>997</v>
+        <v>927</v>
       </c>
       <c r="C1285" t="s">
-        <v>997</v>
+        <v>926</v>
       </c>
     </row>
     <row r="1286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1286" t="s">
-        <v>1001</v>
+        <v>931</v>
       </c>
       <c r="B1286" t="s">
-        <v>1000</v>
+        <v>930</v>
       </c>
       <c r="C1286" t="s">
-        <v>999</v>
+        <v>929</v>
       </c>
     </row>
     <row r="1287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1287" t="s">
-        <v>1004</v>
+        <v>934</v>
       </c>
       <c r="B1287" t="s">
-        <v>1003</v>
+        <v>933</v>
       </c>
       <c r="C1287" t="s">
-        <v>1002</v>
+        <v>932</v>
       </c>
     </row>
     <row r="1288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1288" t="s">
-        <v>1173</v>
+        <v>937</v>
+      </c>
+      <c r="B1288" t="s">
+        <v>936</v>
+      </c>
+      <c r="C1288" t="s">
+        <v>935</v>
       </c>
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1289" t="s">
-        <v>1040</v>
+        <v>940</v>
       </c>
       <c r="B1289" t="s">
-        <v>1041</v>
+        <v>939</v>
       </c>
       <c r="C1289" t="s">
-        <v>1042</v>
+        <v>938</v>
       </c>
     </row>
     <row r="1290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1290" t="s">
-        <v>1043</v>
+        <v>943</v>
       </c>
       <c r="B1290" t="s">
-        <v>1044</v>
+        <v>942</v>
       </c>
       <c r="C1290" t="s">
-        <v>1045</v>
+        <v>941</v>
       </c>
     </row>
     <row r="1291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1291" t="s">
-        <v>1046</v>
+        <v>946</v>
       </c>
       <c r="B1291" t="s">
-        <v>1047</v>
+        <v>945</v>
       </c>
       <c r="C1291" t="s">
-        <v>1048</v>
+        <v>944</v>
       </c>
     </row>
     <row r="1292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1292" t="s">
-        <v>1049</v>
+        <v>948</v>
       </c>
       <c r="B1292" t="s">
-        <v>1050</v>
+        <v>948</v>
       </c>
       <c r="C1292" t="s">
-        <v>1051</v>
+        <v>947</v>
       </c>
     </row>
     <row r="1293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1293" t="s">
-        <v>1052</v>
+        <v>951</v>
       </c>
       <c r="B1293" t="s">
-        <v>1053</v>
+        <v>950</v>
       </c>
       <c r="C1293" t="s">
-        <v>1054</v>
+        <v>949</v>
       </c>
     </row>
     <row r="1294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1294" t="s">
-        <v>1055</v>
+        <v>954</v>
       </c>
       <c r="B1294" t="s">
-        <v>1056</v>
+        <v>953</v>
       </c>
       <c r="C1294" t="s">
-        <v>1057</v>
+        <v>952</v>
       </c>
     </row>
     <row r="1295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1295" t="s">
-        <v>1058</v>
+        <v>957</v>
       </c>
       <c r="B1295" t="s">
-        <v>1059</v>
+        <v>956</v>
       </c>
       <c r="C1295" t="s">
-        <v>1060</v>
+        <v>955</v>
       </c>
     </row>
     <row r="1296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1296" t="s">
-        <v>1061</v>
+        <v>960</v>
       </c>
       <c r="B1296" t="s">
-        <v>1062</v>
+        <v>959</v>
       </c>
       <c r="C1296" t="s">
-        <v>1062</v>
+        <v>958</v>
       </c>
     </row>
     <row r="1297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1297" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B1297" t="s">
-        <v>1064</v>
+        <v>962</v>
       </c>
       <c r="C1297" t="s">
-        <v>1064</v>
+        <v>961</v>
       </c>
     </row>
     <row r="1298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1298" t="s">
-        <v>1065</v>
+        <v>965</v>
       </c>
       <c r="B1298" t="s">
-        <v>1066</v>
+        <v>964</v>
       </c>
       <c r="C1298" t="s">
-        <v>1066</v>
+        <v>963</v>
       </c>
     </row>
     <row r="1299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1299" t="s">
-        <v>1067</v>
+        <v>968</v>
       </c>
       <c r="B1299" t="s">
-        <v>1068</v>
+        <v>967</v>
       </c>
       <c r="C1299" t="s">
-        <v>1068</v>
+        <v>966</v>
       </c>
     </row>
     <row r="1300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1300" t="s">
-        <v>1069</v>
+        <v>965</v>
       </c>
       <c r="B1300" t="s">
-        <v>1070</v>
+        <v>970</v>
       </c>
       <c r="C1300" t="s">
-        <v>1070</v>
+        <v>969</v>
       </c>
     </row>
     <row r="1301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1301" t="s">
-        <v>1071</v>
+        <v>973</v>
       </c>
       <c r="B1301" t="s">
-        <v>1072</v>
+        <v>972</v>
       </c>
       <c r="C1301" t="s">
-        <v>1072</v>
+        <v>971</v>
       </c>
     </row>
     <row r="1302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1302" t="s">
-        <v>1073</v>
+        <v>976</v>
       </c>
       <c r="B1302" t="s">
-        <v>1074</v>
+        <v>975</v>
       </c>
       <c r="C1302" t="s">
-        <v>1074</v>
+        <v>974</v>
       </c>
     </row>
     <row r="1303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1303" t="s">
-        <v>1075</v>
+        <v>979</v>
       </c>
       <c r="B1303" t="s">
-        <v>1076</v>
+        <v>978</v>
       </c>
       <c r="C1303" t="s">
-        <v>1076</v>
+        <v>977</v>
       </c>
     </row>
     <row r="1304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1304" t="s">
-        <v>1077</v>
+        <v>982</v>
       </c>
       <c r="B1304" t="s">
-        <v>1078</v>
+        <v>981</v>
       </c>
       <c r="C1304" t="s">
-        <v>1078</v>
+        <v>980</v>
       </c>
     </row>
     <row r="1305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1305" t="s">
-        <v>1079</v>
+        <v>985</v>
       </c>
       <c r="B1305" t="s">
-        <v>1080</v>
+        <v>984</v>
       </c>
       <c r="C1305" t="s">
-        <v>1080</v>
+        <v>983</v>
       </c>
     </row>
     <row r="1306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1306" t="s">
-        <v>1081</v>
+        <v>988</v>
       </c>
       <c r="B1306" t="s">
-        <v>1082</v>
+        <v>987</v>
       </c>
       <c r="C1306" t="s">
-        <v>1082</v>
+        <v>986</v>
       </c>
     </row>
     <row r="1307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1307" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B1307" t="s">
-        <v>1084</v>
+        <v>990</v>
       </c>
       <c r="C1307" t="s">
-        <v>1084</v>
+        <v>989</v>
       </c>
     </row>
     <row r="1308" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1308" t="s">
-        <v>1085</v>
+        <v>993</v>
       </c>
       <c r="B1308" t="s">
-        <v>1086</v>
+        <v>992</v>
       </c>
       <c r="C1308" t="s">
-        <v>1086</v>
+        <v>991</v>
       </c>
     </row>
     <row r="1309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1309" t="s">
-        <v>1087</v>
+        <v>996</v>
       </c>
       <c r="B1309" t="s">
-        <v>1088</v>
+        <v>995</v>
       </c>
       <c r="C1309" t="s">
-        <v>1088</v>
+        <v>994</v>
       </c>
     </row>
     <row r="1310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1310" t="s">
-        <v>1089</v>
+        <v>998</v>
       </c>
       <c r="B1310" t="s">
-        <v>1090</v>
+        <v>997</v>
       </c>
       <c r="C1310" t="s">
-        <v>1090</v>
+        <v>997</v>
       </c>
     </row>
     <row r="1311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1311" t="s">
-        <v>1091</v>
+        <v>1001</v>
       </c>
       <c r="B1311" t="s">
-        <v>1092</v>
+        <v>1000</v>
       </c>
       <c r="C1311" t="s">
-        <v>1092</v>
+        <v>999</v>
       </c>
     </row>
     <row r="1312" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1312" t="s">
-        <v>1093</v>
+        <v>1004</v>
       </c>
       <c r="B1312" t="s">
-        <v>1094</v>
+        <v>1003</v>
       </c>
       <c r="C1312" t="s">
-        <v>1094</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="1313" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1313" t="s">
-        <v>1095</v>
-      </c>
-      <c r="B1313" t="s">
-        <v>1096</v>
-      </c>
-      <c r="C1313" t="s">
-        <v>1096</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="1314" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1314" t="s">
-        <v>1097</v>
+        <v>1040</v>
       </c>
       <c r="B1314" t="s">
-        <v>1098</v>
+        <v>1041</v>
       </c>
       <c r="C1314" t="s">
-        <v>1098</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="1315" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1315" t="s">
-        <v>1099</v>
+        <v>1043</v>
       </c>
       <c r="B1315" t="s">
-        <v>1100</v>
+        <v>1044</v>
       </c>
       <c r="C1315" t="s">
-        <v>1101</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="1316" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1316" t="s">
-        <v>1102</v>
+        <v>1046</v>
       </c>
       <c r="B1316" t="s">
-        <v>1103</v>
+        <v>1047</v>
       </c>
       <c r="C1316" t="s">
-        <v>1104</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="1317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1317" t="s">
-        <v>1105</v>
+        <v>1049</v>
       </c>
       <c r="B1317" t="s">
-        <v>1106</v>
+        <v>1050</v>
       </c>
       <c r="C1317" t="s">
-        <v>1107</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="1318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1318" t="s">
-        <v>1108</v>
+        <v>1052</v>
       </c>
       <c r="B1318" t="s">
-        <v>1109</v>
+        <v>1053</v>
       </c>
       <c r="C1318" t="s">
-        <v>1110</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="1319" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1319" t="s">
-        <v>1111</v>
+        <v>1055</v>
       </c>
       <c r="B1319" t="s">
-        <v>1112</v>
+        <v>1056</v>
       </c>
       <c r="C1319" t="s">
-        <v>1113</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="1320" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1320" t="s">
-        <v>1114</v>
+        <v>1058</v>
       </c>
       <c r="B1320" t="s">
-        <v>1115</v>
+        <v>1059</v>
       </c>
       <c r="C1320" t="s">
-        <v>1116</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="1321" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1321" t="s">
-        <v>1117</v>
+        <v>1061</v>
       </c>
       <c r="B1321" t="s">
-        <v>1118</v>
+        <v>1062</v>
       </c>
       <c r="C1321" t="s">
-        <v>1119</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="1322" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1322" t="s">
-        <v>1120</v>
+        <v>1063</v>
       </c>
       <c r="B1322" t="s">
-        <v>1121</v>
+        <v>1064</v>
       </c>
       <c r="C1322" t="s">
-        <v>1122</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="1323" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1323" t="s">
-        <v>1123</v>
+        <v>1065</v>
       </c>
       <c r="B1323" t="s">
-        <v>1124</v>
+        <v>1066</v>
       </c>
       <c r="C1323" t="s">
-        <v>1125</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="1324" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1324" t="s">
-        <v>2124</v>
+        <v>1067</v>
+      </c>
+      <c r="B1324" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C1324" t="s">
+        <v>1068</v>
       </c>
     </row>
     <row r="1325" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1325" s="4" t="s">
-        <v>2116</v>
-      </c>
-      <c r="B1325" s="4" t="s">
-        <v>2125</v>
+      <c r="A1325" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B1325" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C1325" t="s">
+        <v>1070</v>
       </c>
     </row>
     <row r="1326" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1326" s="4" t="s">
-        <v>2117</v>
-      </c>
-      <c r="B1326" s="4" t="s">
-        <v>2126</v>
+      <c r="A1326" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B1326" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C1326" t="s">
+        <v>1072</v>
       </c>
     </row>
     <row r="1327" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1327" s="4" t="s">
-        <v>2118</v>
-      </c>
-      <c r="B1327" s="4" t="s">
-        <v>2127</v>
+      <c r="A1327" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B1327" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C1327" t="s">
+        <v>1074</v>
       </c>
     </row>
     <row r="1328" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1328" s="4" t="s">
-        <v>2119</v>
-      </c>
-      <c r="B1328" s="4" t="s">
-        <v>2128</v>
+      <c r="A1328" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B1328" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C1328" t="s">
+        <v>1076</v>
       </c>
     </row>
     <row r="1329" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1329" s="5" t="s">
-        <v>2120</v>
-      </c>
-      <c r="B1329" s="5" t="s">
-        <v>2129</v>
+      <c r="A1329" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B1329" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C1329" t="s">
+        <v>1078</v>
       </c>
     </row>
     <row r="1330" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1330" t="s">
-        <v>2130</v>
+        <v>1079</v>
       </c>
       <c r="B1330" t="s">
-        <v>2131</v>
+        <v>1080</v>
       </c>
       <c r="C1330" t="s">
-        <v>730</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="1331" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1331" t="s">
-        <v>2132</v>
+        <v>1081</v>
       </c>
       <c r="B1331" t="s">
-        <v>2133</v>
+        <v>1082</v>
       </c>
       <c r="C1331" t="s">
-        <v>849</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="1332" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1332" t="s">
-        <v>2134</v>
+        <v>1083</v>
       </c>
       <c r="B1332" t="s">
-        <v>2135</v>
+        <v>1084</v>
       </c>
       <c r="C1332" t="s">
-        <v>2121</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1333" t="s">
-        <v>2136</v>
+        <v>1085</v>
       </c>
       <c r="B1333" t="s">
-        <v>2137</v>
+        <v>1086</v>
       </c>
       <c r="C1333" t="s">
-        <v>763</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="1334" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1334" t="s">
-        <v>2138</v>
+        <v>1087</v>
       </c>
       <c r="B1334" t="s">
-        <v>2139</v>
+        <v>1088</v>
       </c>
       <c r="C1334" t="s">
-        <v>2122</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="1335" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1335" t="s">
-        <v>2140</v>
+        <v>1089</v>
       </c>
       <c r="B1335" t="s">
-        <v>2141</v>
+        <v>1090</v>
       </c>
       <c r="C1335" t="s">
-        <v>852</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="1336" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1336" t="s">
-        <v>2142</v>
+        <v>1091</v>
       </c>
       <c r="B1336" t="s">
-        <v>2143</v>
+        <v>1092</v>
       </c>
       <c r="C1336" t="s">
-        <v>2123</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="1337" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1337" t="s">
-        <v>2144</v>
+        <v>1093</v>
       </c>
       <c r="B1337" t="s">
-        <v>2145</v>
+        <v>1094</v>
       </c>
       <c r="C1337" t="s">
-        <v>1573</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="1338" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1338" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B1338" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C1338" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1339" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B1339" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C1339" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1340" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B1340" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C1340" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1341" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B1341" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C1341" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1342" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B1342" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C1342" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1343" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B1343" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C1343" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1344" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B1344" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C1344" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1345" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B1345" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C1345" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1346" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B1346" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C1346" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1347" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B1347" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C1347" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1348" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B1348" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C1348" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1349" t="s">
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1350" s="4" t="s">
+        <v>2116</v>
+      </c>
+      <c r="B1350" s="4" t="s">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1351" s="4" t="s">
+        <v>2117</v>
+      </c>
+      <c r="B1351" s="4" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1352" s="4" t="s">
+        <v>2118</v>
+      </c>
+      <c r="B1352" s="4" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1353" s="4" t="s">
+        <v>2119</v>
+      </c>
+      <c r="B1353" s="4" t="s">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1354" s="5" t="s">
+        <v>2120</v>
+      </c>
+      <c r="B1354" s="5" t="s">
+        <v>2129</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1355" t="s">
+        <v>2130</v>
+      </c>
+      <c r="B1355" t="s">
+        <v>2131</v>
+      </c>
+      <c r="C1355" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1356" t="s">
+        <v>2132</v>
+      </c>
+      <c r="B1356" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1356" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1357" t="s">
+        <v>2134</v>
+      </c>
+      <c r="B1357" t="s">
+        <v>2135</v>
+      </c>
+      <c r="C1357" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1358" t="s">
+        <v>2136</v>
+      </c>
+      <c r="B1358" t="s">
+        <v>2137</v>
+      </c>
+      <c r="C1358" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1359" t="s">
+        <v>2138</v>
+      </c>
+      <c r="B1359" t="s">
+        <v>2139</v>
+      </c>
+      <c r="C1359" t="s">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1360" t="s">
+        <v>2140</v>
+      </c>
+      <c r="B1360" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1360" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1361" t="s">
+        <v>2142</v>
+      </c>
+      <c r="B1361" t="s">
+        <v>2143</v>
+      </c>
+      <c r="C1361" t="s">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1362" t="s">
+        <v>2144</v>
+      </c>
+      <c r="B1362" t="s">
+        <v>2145</v>
+      </c>
+      <c r="C1362" t="s">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1363" t="s">
         <v>2146</v>
       </c>
-      <c r="B1338" t="s">
+      <c r="B1363" t="s">
         <v>2147</v>
       </c>
-      <c r="C1338" t="s">
+      <c r="C1363" t="s">
         <v>742</v>
       </c>
     </row>

--- a/00-日文單字.xlsx
+++ b/00-日文單字.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://guandamachine-my.sharepoint.com/personal/ec03_gd_guandamachine_com_tw/Documents/Fly/日語/日語練習網站/database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="226" documentId="11_AD4DBB64A54DDB1B405E38AFBD9A2E1F4F90DF1A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DF05A15-5B80-4E88-863B-140CDCB716AC}"/>
+  <xr:revisionPtr revIDLastSave="229" documentId="11_AD4DBB64A54DDB1B405E38AFBD9A2E1F4F90DF1A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52CF6432-6BBF-4B77-AA47-FC55AE5C65DE}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -9502,15 +9502,6 @@
     <t>送[人](去某處)</t>
   </si>
   <si>
-    <t>おくります ひとを～</t>
-  </si>
-  <si>
-    <t>送ります 人を～</t>
-  </si>
-  <si>
-    <t xml:space="preserve">送[人](去某處) </t>
-  </si>
-  <si>
     <t>しょうかいします</t>
   </si>
   <si>
@@ -9644,6 +9635,18 @@
   </si>
   <si>
     <t>母親節</t>
+  </si>
+  <si>
+    <t>人を 送ります</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ひとを おくります</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">送[某人](去某處) </t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -20244,201 +20247,201 @@
     </row>
     <row r="1039" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1039" t="s">
-        <v>3090</v>
+        <v>3136</v>
       </c>
       <c r="B1039" t="s">
-        <v>3091</v>
+        <v>3135</v>
       </c>
       <c r="C1039" t="s">
-        <v>3092</v>
+        <v>3137</v>
       </c>
     </row>
     <row r="1040" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1040" t="s">
-        <v>3093</v>
+        <v>3090</v>
       </c>
       <c r="B1040" t="s">
-        <v>3094</v>
+        <v>3091</v>
       </c>
       <c r="C1040" t="s">
-        <v>3095</v>
+        <v>3092</v>
       </c>
     </row>
     <row r="1041" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1041" t="s">
-        <v>3096</v>
+        <v>3093</v>
       </c>
       <c r="B1041" t="s">
-        <v>3097</v>
+        <v>3094</v>
       </c>
       <c r="C1041" t="s">
-        <v>3098</v>
+        <v>3095</v>
       </c>
     </row>
     <row r="1042" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1042" t="s">
-        <v>3099</v>
+        <v>3096</v>
       </c>
       <c r="B1042" t="s">
-        <v>3100</v>
+        <v>3097</v>
       </c>
       <c r="C1042" t="s">
-        <v>3101</v>
+        <v>3098</v>
       </c>
     </row>
     <row r="1043" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1043" t="s">
-        <v>3102</v>
+        <v>3099</v>
       </c>
       <c r="C1043" t="s">
-        <v>3103</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="1044" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1044" t="s">
-        <v>3104</v>
+        <v>3101</v>
       </c>
       <c r="C1044" t="s">
-        <v>3103</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="1045" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1045" t="s">
-        <v>3105</v>
+        <v>3102</v>
       </c>
       <c r="C1045" t="s">
-        <v>3106</v>
+        <v>3103</v>
       </c>
     </row>
     <row r="1046" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1046" t="s">
-        <v>3107</v>
+        <v>3104</v>
       </c>
       <c r="C1046" t="s">
-        <v>3106</v>
+        <v>3103</v>
       </c>
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1047" t="s">
-        <v>3108</v>
+        <v>3105</v>
       </c>
       <c r="C1047" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
     </row>
     <row r="1048" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1048" t="s">
-        <v>3110</v>
+        <v>3107</v>
       </c>
       <c r="C1048" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
     </row>
     <row r="1049" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1049" t="s">
-        <v>3111</v>
+        <v>3108</v>
       </c>
       <c r="B1049" t="s">
-        <v>3112</v>
+        <v>3109</v>
       </c>
       <c r="C1049" t="s">
-        <v>3112</v>
+        <v>3109</v>
       </c>
     </row>
     <row r="1050" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1050" t="s">
-        <v>3113</v>
+        <v>3110</v>
       </c>
       <c r="B1050" t="s">
-        <v>3114</v>
+        <v>3111</v>
       </c>
       <c r="C1050" t="s">
-        <v>3115</v>
+        <v>3112</v>
       </c>
     </row>
     <row r="1051" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1051" t="s">
-        <v>3116</v>
+        <v>3113</v>
       </c>
       <c r="B1051" t="s">
-        <v>3117</v>
+        <v>3114</v>
       </c>
       <c r="C1051" t="s">
-        <v>3118</v>
+        <v>3115</v>
       </c>
     </row>
     <row r="1052" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1052" t="s">
-        <v>3119</v>
+        <v>3116</v>
       </c>
       <c r="B1052" t="s">
-        <v>3120</v>
+        <v>3117</v>
       </c>
       <c r="C1052" t="s">
-        <v>3121</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="1053" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1053" t="s">
-        <v>3122</v>
+        <v>3119</v>
       </c>
       <c r="B1053" t="s">
-        <v>3123</v>
+        <v>3120</v>
       </c>
       <c r="C1053" t="s">
-        <v>3123</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="1054" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1054" t="s">
-        <v>3124</v>
+        <v>3121</v>
       </c>
       <c r="B1054" t="s">
-        <v>3125</v>
+        <v>3122</v>
       </c>
       <c r="C1054" t="s">
-        <v>3126</v>
+        <v>3123</v>
       </c>
     </row>
     <row r="1055" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1055" t="s">
-        <v>3127</v>
+        <v>3124</v>
       </c>
       <c r="C1055" t="s">
-        <v>3128</v>
+        <v>3125</v>
       </c>
     </row>
     <row r="1056" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1056" t="s">
-        <v>3129</v>
+        <v>3126</v>
       </c>
       <c r="B1056" t="s">
-        <v>3130</v>
+        <v>3127</v>
       </c>
       <c r="C1056" t="s">
-        <v>3131</v>
+        <v>3128</v>
       </c>
     </row>
     <row r="1057" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1057" t="s">
-        <v>3132</v>
+        <v>3129</v>
       </c>
       <c r="B1057" t="s">
-        <v>3133</v>
+        <v>3130</v>
       </c>
       <c r="C1057" t="s">
-        <v>3134</v>
+        <v>3131</v>
       </c>
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1058" t="s">
-        <v>3135</v>
+        <v>3132</v>
       </c>
       <c r="B1058" t="s">
-        <v>3136</v>
+        <v>3133</v>
       </c>
       <c r="C1058" t="s">
-        <v>3137</v>
+        <v>3134</v>
       </c>
     </row>
     <row r="1059" spans="1:3" x14ac:dyDescent="0.3">
